--- a/data/export/2026-09-25-operations.xlsx
+++ b/data/export/2026-09-25-operations.xlsx
@@ -427,13 +427,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD21"/>
+  <dimension ref="A1:AD47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -442,7 +442,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
     <col width="26" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
     <col width="22" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
@@ -643,32 +643,36 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:13</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -676,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -700,33 +704,37 @@
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC2" s="2" t="inlineStr"/>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -759,32 +767,36 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -792,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -816,33 +828,37 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC3" s="2" t="inlineStr"/>
+      <c r="AC3" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -875,32 +891,36 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:39</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -908,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -932,33 +952,37 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC4" s="2" t="inlineStr"/>
+      <c r="AC4" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1048,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1063,7 +1087,7 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
@@ -1074,7 +1098,7 @@
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1107,32 +1131,36 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1140,7 +1168,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1164,33 +1192,37 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1288,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1306,7 +1338,7 @@
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1404,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1422,7 +1454,7 @@
       <c r="AC8" s="2" t="inlineStr"/>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1435,22 +1467,22 @@
       <c r="B9" s="2" t="inlineStr"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>沪A13735A</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>07:05</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>07:15</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1488,7 +1520,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1502,7 +1534,7 @@
       <c r="U9" s="2" t="inlineStr"/>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:05</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -1538,35 +1570,35 @@
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1604,7 +1636,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1618,7 +1650,7 @@
       <c r="U10" s="2" t="inlineStr"/>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1654,35 +1686,35 @@
       <c r="AC10" s="2" t="inlineStr"/>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1715,12 +1747,12 @@
       <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1734,7 +1766,7 @@
       <c r="U11" s="2" t="inlineStr"/>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1770,35 +1802,35 @@
       <c r="AC11" s="2" t="inlineStr"/>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1836,7 +1868,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1850,7 +1882,7 @@
       <c r="U12" s="2" t="inlineStr"/>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1875,46 +1907,50 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>沪A57051D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1952,7 +1988,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1966,7 +2002,7 @@
       <c r="U13" s="2" t="inlineStr"/>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1991,46 +2027,50 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2068,7 +2108,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2082,7 +2122,7 @@
       <c r="U14" s="2" t="inlineStr"/>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2107,46 +2147,50 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2179,12 +2223,12 @@
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2198,7 +2242,7 @@
       <c r="U15" s="2" t="inlineStr"/>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
@@ -2234,35 +2278,35 @@
       <c r="AC15" s="2" t="inlineStr"/>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2295,12 +2339,12 @@
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2314,7 +2358,7 @@
       <c r="U16" s="2" t="inlineStr"/>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2339,7 +2383,7 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
@@ -2350,35 +2394,35 @@
       <c r="AC16" s="2" t="inlineStr"/>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2411,12 +2455,12 @@
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2430,7 +2474,7 @@
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2455,18 +2499,22 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -2479,22 +2527,22 @@
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>06:05</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2527,12 +2575,12 @@
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2546,7 +2594,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2582,35 +2630,35 @@
       <c r="AC18" s="2" t="inlineStr"/>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2643,12 +2691,12 @@
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2662,7 +2710,7 @@
       <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2698,35 +2746,35 @@
       <c r="AC19" s="2" t="inlineStr"/>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2759,12 +2807,12 @@
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2778,7 +2826,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2814,35 +2862,35 @@
       <c r="AC20" s="2" t="inlineStr"/>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A57051D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2875,12 +2923,12 @@
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2894,7 +2942,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2930,7 +2978,3031 @@
       <c r="AC21" s="2" t="inlineStr"/>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr"/>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr"/>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr"/>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr"/>
+      <c r="AD22" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr"/>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr"/>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AD23" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr"/>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AD24" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr"/>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr"/>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AD25" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr"/>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr"/>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AD26" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr"/>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr"/>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr"/>
+      <c r="AD27" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr"/>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr"/>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr"/>
+      <c r="AD28" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr"/>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr"/>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AD29" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr"/>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr"/>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AD30" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr"/>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr"/>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AD31" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr"/>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr"/>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AD32" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr"/>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr"/>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AD33" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr"/>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr"/>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AD34" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr"/>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr"/>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr"/>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AD35" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr"/>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr"/>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr"/>
+      <c r="AD36" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr"/>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr"/>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr"/>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr"/>
+      <c r="AD37" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr"/>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr"/>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr"/>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr"/>
+      <c r="AD38" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr"/>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr"/>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr"/>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr"/>
+      <c r="AD39" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr"/>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>08:27</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>87分钟</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr"/>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AD40" s="2" t="inlineStr">
+        <is>
+          <t>1/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr"/>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr"/>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr"/>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr"/>
+      <c r="AD41" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr"/>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr"/>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr"/>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr"/>
+      <c r="AD42" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr"/>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr"/>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr"/>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr"/>
+      <c r="AD43" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr"/>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr"/>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr"/>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr"/>
+      <c r="AD44" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr"/>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr"/>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr"/>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr"/>
+      <c r="AD45" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr"/>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr"/>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr"/>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr"/>
+      <c r="AD46" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr"/>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr"/>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr"/>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr"/>
+      <c r="AD47" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-25-operations.xlsx
+++ b/data/export/2026-09-25-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD47"/>
+  <dimension ref="A1:AD71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -724,17 +724,17 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -1015,32 +1015,36 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1048,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1072,17 +1076,17 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1092,13 +1096,17 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC5" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC5" s="2" t="inlineStr">
+        <is>
+          <t>67.0</t>
+        </is>
+      </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -1141,24 +1149,24 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>07:43</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1168,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1217,12 +1225,12 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1263,36 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -1288,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1312,33 +1324,37 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -1371,32 +1387,36 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1404,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1428,33 +1448,37 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1511,36 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1520,7 +1548,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1544,33 +1572,37 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -1603,32 +1635,36 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1636,7 +1672,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1660,33 +1696,37 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -1719,32 +1759,36 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -1752,7 +1796,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1776,33 +1820,37 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1835,32 +1883,36 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1868,7 +1920,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1892,17 +1944,17 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1912,17 +1964,17 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -1988,7 +2040,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2027,7 +2079,7 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
@@ -2042,7 +2094,7 @@
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2160,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2147,7 +2199,7 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
@@ -2162,7 +2214,7 @@
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2280,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2344,7 +2396,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2388,13 +2440,17 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC16" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>67.0</t>
+        </is>
+      </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -2460,7 +2516,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2509,40 +2565,40 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2575,12 +2631,12 @@
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2594,7 +2650,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2619,46 +2675,50 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2696,7 +2756,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2710,7 +2770,7 @@
       <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2735,46 +2795,50 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2812,7 +2876,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2826,7 +2890,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2851,46 +2915,50 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A57051D</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2923,12 +2991,12 @@
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2942,7 +3010,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2967,46 +3035,50 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -3044,7 +3116,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3058,7 +3130,7 @@
       <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3083,46 +3155,50 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3160,7 +3236,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3174,7 +3250,7 @@
       <c r="U23" s="2" t="inlineStr"/>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3199,46 +3275,50 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3271,12 +3351,12 @@
       <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3290,7 +3370,7 @@
       <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3315,18 +3395,22 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -3339,7 +3423,7 @@
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -3349,7 +3433,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -3387,12 +3471,12 @@
       <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3406,7 +3490,7 @@
       <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3431,7 +3515,7 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
@@ -3442,7 +3526,7 @@
       <c r="AC25" s="2" t="inlineStr"/>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -3455,7 +3539,7 @@
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -3465,7 +3549,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3475,40 +3559,44 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3522,7 +3610,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3532,33 +3620,37 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>123.0</t>
+        </is>
+      </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>3/26</t>
         </is>
       </c>
     </row>
@@ -3571,7 +3663,7 @@
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3581,7 +3673,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3591,40 +3683,44 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3638,7 +3734,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3648,17 +3744,17 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3668,13 +3764,17 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC27" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>122.0</t>
+        </is>
+      </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>2/26</t>
         </is>
       </c>
     </row>
@@ -3687,7 +3787,7 @@
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A57051D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -3697,7 +3797,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -3707,40 +3807,44 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3754,7 +3858,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3764,33 +3868,37 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC28" s="2" t="inlineStr"/>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>4/26</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3911,7 @@
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -3813,7 +3921,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3823,40 +3931,44 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>121分钟</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3870,7 +3982,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3880,17 +3992,17 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3900,13 +4012,17 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC29" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>121.0</t>
+        </is>
+      </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>1/26</t>
         </is>
       </c>
     </row>
@@ -3919,7 +4035,7 @@
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -3929,7 +4045,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -3967,12 +4083,12 @@
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3986,7 +4102,7 @@
       <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4022,7 +4138,7 @@
       <c r="AC30" s="2" t="inlineStr"/>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -4035,7 +4151,7 @@
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -4045,7 +4161,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -4083,12 +4199,12 @@
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4102,7 +4218,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4138,7 +4254,7 @@
       <c r="AC31" s="2" t="inlineStr"/>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -4151,22 +4267,22 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -4199,12 +4315,12 @@
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4218,7 +4334,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4254,7 +4370,7 @@
       <c r="AC32" s="2" t="inlineStr"/>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -4267,7 +4383,7 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -4277,7 +4393,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -4315,12 +4431,12 @@
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4334,7 +4450,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4370,7 +4486,7 @@
       <c r="AC33" s="2" t="inlineStr"/>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -4383,7 +4499,7 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -4393,7 +4509,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -4431,12 +4547,12 @@
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4450,7 +4566,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4486,7 +4602,7 @@
       <c r="AC34" s="2" t="inlineStr"/>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -4499,22 +4615,22 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4547,12 +4663,12 @@
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4566,7 +4682,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4602,7 +4718,7 @@
       <c r="AC35" s="2" t="inlineStr"/>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -4615,22 +4731,22 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4663,12 +4779,12 @@
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4682,7 +4798,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4718,35 +4834,35 @@
       <c r="AC36" s="2" t="inlineStr"/>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4779,12 +4895,12 @@
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4798,7 +4914,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4823,7 +4939,7 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
@@ -4834,35 +4950,35 @@
       <c r="AC37" s="2" t="inlineStr"/>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4895,12 +5011,12 @@
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4914,7 +5030,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -4939,7 +5055,7 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
@@ -4950,35 +5066,35 @@
       <c r="AC38" s="2" t="inlineStr"/>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -5011,12 +5127,12 @@
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5030,7 +5146,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5066,77 +5182,73 @@
       <c r="AC39" s="2" t="inlineStr"/>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr"/>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5150,7 +5262,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5160,17 +5272,17 @@
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5180,45 +5292,41 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC40" s="2" t="inlineStr">
-        <is>
-          <t>87.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr"/>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>1/9</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -5251,12 +5359,12 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5270,7 +5378,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5306,35 +5414,35 @@
       <c r="AC41" s="2" t="inlineStr"/>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5367,12 +5475,12 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5386,7 +5494,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5422,35 +5530,35 @@
       <c r="AC42" s="2" t="inlineStr"/>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5483,12 +5591,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5502,7 +5610,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5538,35 +5646,35 @@
       <c r="AC43" s="2" t="inlineStr"/>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5599,12 +5707,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5618,7 +5726,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5643,7 +5751,7 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
@@ -5654,35 +5762,35 @@
       <c r="AC44" s="2" t="inlineStr"/>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5715,12 +5823,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5734,7 +5842,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5770,35 +5878,35 @@
       <c r="AC45" s="2" t="inlineStr"/>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5831,12 +5939,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5850,7 +5958,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5886,35 +5994,35 @@
       <c r="AC46" s="2" t="inlineStr"/>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5947,12 +6055,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5966,7 +6074,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -5991,7 +6099,7 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
@@ -6002,7 +6110,2867 @@
       <c r="AC47" s="2" t="inlineStr"/>
       <c r="AD47" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr"/>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr"/>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr"/>
+      <c r="AD48" s="2" t="inlineStr">
+        <is>
+          <t>—/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr"/>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr"/>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr"/>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr"/>
+      <c r="AD49" s="2" t="inlineStr">
+        <is>
+          <t>—/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr"/>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr"/>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr"/>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr"/>
+      <c r="AD50" s="2" t="inlineStr">
+        <is>
+          <t>—/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr"/>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr"/>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr"/>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>123.0</t>
+        </is>
+      </c>
+      <c r="AD51" s="2" t="inlineStr">
+        <is>
+          <t>3/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr"/>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr"/>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr"/>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr"/>
+      <c r="AD52" s="2" t="inlineStr">
+        <is>
+          <t>—/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr"/>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>沪A57051D</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr"/>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr"/>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AD53" s="2" t="inlineStr">
+        <is>
+          <t>4/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr"/>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr"/>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr"/>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr"/>
+      <c r="AD54" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr"/>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>71分钟</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr"/>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="AD55" s="2" t="inlineStr">
+        <is>
+          <t>1/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr"/>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>08:08</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>83分钟</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr"/>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AD56" s="2" t="inlineStr">
+        <is>
+          <t>2/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr"/>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>85分钟</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr"/>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr"/>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AD57" s="2" t="inlineStr">
+        <is>
+          <t>4/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr"/>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>08:36</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>86分钟</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr"/>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AD58" s="2" t="inlineStr">
+        <is>
+          <t>5/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr"/>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>08:43</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>83分钟</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr"/>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr"/>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AD59" s="2" t="inlineStr">
+        <is>
+          <t>2/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr"/>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>98分钟</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr"/>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
+      <c r="AD60" s="2" t="inlineStr">
+        <is>
+          <t>6/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr"/>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr"/>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr"/>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr"/>
+      <c r="AD61" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr"/>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr"/>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr"/>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr"/>
+      <c r="AD62" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr"/>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr"/>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr"/>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr"/>
+      <c r="AD63" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr"/>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr"/>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr"/>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AD64" s="2" t="inlineStr">
+        <is>
+          <t>2/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr"/>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr"/>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr"/>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="AD65" s="2" t="inlineStr">
+        <is>
+          <t>1/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr"/>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr"/>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr"/>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr"/>
+      <c r="AD66" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr"/>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr"/>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr"/>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AD67" s="2" t="inlineStr">
+        <is>
+          <t>4/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr"/>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr"/>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr"/>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr"/>
+      <c r="AD68" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr"/>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr"/>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr"/>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr"/>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AD69" s="2" t="inlineStr">
+        <is>
+          <t>5/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr"/>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr"/>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr"/>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr"/>
+      <c r="AD70" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr"/>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr"/>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr"/>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AD71" s="2" t="inlineStr">
+        <is>
+          <t>2/12</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-25-operations.xlsx
+++ b/data/export/2026-09-25-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD71"/>
+  <dimension ref="A1:AD95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -729,12 +729,12 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -848,17 +848,17 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1091,22 +1091,22 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1215,22 +1215,22 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1339,22 +1339,22 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -1893,24 +1893,24 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -2007,32 +2007,36 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2040,7 +2044,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2064,17 +2068,17 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2084,17 +2088,17 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -2127,32 +2131,36 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2160,7 +2168,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2184,17 +2192,17 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2204,12 +2212,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AD14" s="2" t="inlineStr">
@@ -2247,32 +2255,36 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -2280,7 +2292,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2304,33 +2316,37 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -2363,32 +2379,36 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2396,7 +2416,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2420,37 +2440,37 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -2483,32 +2503,36 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2516,7 +2540,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2540,37 +2564,37 @@
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -2603,32 +2627,36 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -2636,7 +2664,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2660,37 +2688,37 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2784,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2795,7 +2823,7 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
@@ -2810,7 +2838,7 @@
       </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -2876,7 +2904,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2930,7 +2958,7 @@
       </c>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -2996,7 +3024,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3035,7 +3063,7 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
@@ -3050,7 +3078,7 @@
       </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3144,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3155,7 +3183,7 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
@@ -3170,7 +3198,7 @@
       </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3264,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3280,17 +3308,17 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -3303,22 +3331,22 @@
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>沪A67353D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>09:18</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3351,12 +3379,12 @@
       <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3370,7 +3398,7 @@
       <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3395,7 +3423,7 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
@@ -3405,40 +3433,40 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3476,7 +3504,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3490,7 +3518,7 @@
       <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3515,80 +3543,80 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>73.5</t>
+        </is>
+      </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>123分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3596,7 +3624,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3610,7 +3638,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3620,99 +3648,95 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>3/26</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>122分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3720,7 +3744,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3734,7 +3758,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3744,99 +3768,95 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>2/26</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A57051D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3844,7 +3864,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3858,7 +3878,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3868,22 +3888,22 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
@@ -3893,82 +3913,78 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>4/26</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>121分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3982,7 +3998,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3992,65 +4008,65 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>1/26</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -4088,7 +4104,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4102,7 +4118,7 @@
       <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4127,46 +4143,50 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -4199,12 +4219,12 @@
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4218,7 +4238,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4243,18 +4263,22 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -4267,7 +4291,7 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -4277,7 +4301,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -4315,12 +4339,12 @@
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4334,7 +4358,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4359,7 +4383,7 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
@@ -4370,7 +4394,7 @@
       <c r="AC32" s="2" t="inlineStr"/>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4383,7 +4407,7 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -4393,7 +4417,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -4403,40 +4427,44 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr"/>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4450,7 +4478,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4460,33 +4488,37 @@
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB33" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>123.0</t>
+        </is>
+      </c>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -4499,7 +4531,7 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -4509,7 +4541,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -4519,40 +4551,44 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4566,7 +4602,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4576,33 +4612,37 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>122.0</t>
+        </is>
+      </c>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -4615,7 +4655,7 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A57051D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -4625,7 +4665,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -4635,40 +4675,44 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr"/>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4682,7 +4726,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4692,33 +4736,37 @@
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4779,7 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -4741,7 +4789,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -4751,40 +4799,44 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr"/>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4798,7 +4850,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4808,33 +4860,37 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC36" s="2" t="inlineStr"/>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -4847,7 +4903,7 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -4857,7 +4913,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -4867,40 +4923,44 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4914,7 +4974,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4924,33 +4984,37 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC37" s="2" t="inlineStr"/>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
@@ -4963,7 +5027,7 @@
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -4973,7 +5037,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -4983,40 +5047,44 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5030,7 +5098,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -5040,33 +5108,37 @@
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB38" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC38" s="2" t="inlineStr"/>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -5079,60 +5151,64 @@
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr"/>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5146,7 +5222,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5156,33 +5232,37 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB39" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC39" s="2" t="inlineStr"/>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>10/27</t>
         </is>
       </c>
     </row>
@@ -5195,7 +5275,7 @@
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -5205,7 +5285,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -5215,40 +5295,44 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr"/>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5262,7 +5346,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5272,33 +5356,37 @@
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC40" s="2" t="inlineStr"/>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
@@ -5311,7 +5399,7 @@
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -5321,7 +5409,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -5331,40 +5419,44 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr"/>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5378,7 +5470,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5388,17 +5480,17 @@
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5408,13 +5500,17 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC41" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -5427,60 +5523,64 @@
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr"/>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5494,7 +5594,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5504,33 +5604,37 @@
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB42" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC42" s="2" t="inlineStr"/>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>11/27</t>
         </is>
       </c>
     </row>
@@ -5543,60 +5647,64 @@
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr"/>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5610,7 +5718,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5620,17 +5728,17 @@
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5640,13 +5748,17 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC43" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -5659,7 +5771,7 @@
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -5669,7 +5781,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -5707,12 +5819,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5726,7 +5838,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5751,7 +5863,7 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
@@ -5762,7 +5874,7 @@
       <c r="AC44" s="2" t="inlineStr"/>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -5775,7 +5887,7 @@
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -5785,7 +5897,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -5823,12 +5935,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5842,7 +5954,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5878,7 +5990,7 @@
       <c r="AC45" s="2" t="inlineStr"/>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -5891,22 +6003,22 @@
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5939,12 +6051,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5958,7 +6070,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5994,7 +6106,7 @@
       <c r="AC46" s="2" t="inlineStr"/>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -6007,7 +6119,7 @@
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -6017,7 +6129,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -6055,12 +6167,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6074,7 +6186,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -6110,7 +6222,7 @@
       <c r="AC47" s="2" t="inlineStr"/>
       <c r="AD47" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -6123,22 +6235,22 @@
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>08:28</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -6171,12 +6283,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6190,7 +6302,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6226,7 +6338,7 @@
       <c r="AC48" s="2" t="inlineStr"/>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -6239,7 +6351,7 @@
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -6249,7 +6361,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -6287,12 +6399,12 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6306,7 +6418,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6342,7 +6454,7 @@
       <c r="AC49" s="2" t="inlineStr"/>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -6355,7 +6467,7 @@
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -6365,7 +6477,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -6403,12 +6515,12 @@
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6422,7 +6534,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6447,7 +6559,7 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
@@ -6458,7 +6570,7 @@
       <c r="AC50" s="2" t="inlineStr"/>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -6471,22 +6583,22 @@
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6524,7 +6636,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6538,7 +6650,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6563,22 +6675,18 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC51" s="2" t="inlineStr">
-        <is>
-          <t>123.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr"/>
       <c r="AD51" s="2" t="inlineStr">
         <is>
-          <t>3/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -6591,22 +6699,22 @@
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>08:48</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6639,12 +6747,12 @@
       <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6658,7 +6766,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6694,7 +6802,7 @@
       <c r="AC52" s="2" t="inlineStr"/>
       <c r="AD52" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -6707,7 +6815,7 @@
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A57051D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -6717,7 +6825,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -6760,7 +6868,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6774,7 +6882,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6799,50 +6907,46 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC53" s="2" t="inlineStr">
-        <is>
-          <t>129.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr"/>
       <c r="AD53" s="2" t="inlineStr">
         <is>
-          <t>4/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6875,12 +6979,12 @@
       <c r="N54" s="2" t="inlineStr"/>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6894,7 +6998,7 @@
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -6919,7 +7023,7 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
@@ -6930,77 +7034,73 @@
       <c r="AC54" s="2" t="inlineStr"/>
       <c r="AD54" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr"/>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
-        </is>
-      </c>
-      <c r="N55" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr"/>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7014,7 +7114,7 @@
       <c r="U55" s="2" t="inlineStr"/>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -7024,107 +7124,99 @@
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC55" s="2" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr"/>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr"/>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N56" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr"/>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7138,7 +7230,7 @@
       <c r="U56" s="2" t="inlineStr"/>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -7148,107 +7240,99 @@
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC56" s="2" t="inlineStr">
-        <is>
-          <t>83.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr"/>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr"/>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N57" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr"/>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7262,7 +7346,7 @@
       <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
@@ -7272,17 +7356,17 @@
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
@@ -7292,87 +7376,79 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC57" s="2" t="inlineStr">
-        <is>
-          <t>85.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr"/>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>08:36</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr"/>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N58" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr"/>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7386,7 +7462,7 @@
       <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
@@ -7396,17 +7472,17 @@
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7421,82 +7497,78 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>5/12</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr"/>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N59" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr"/>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7510,7 +7582,7 @@
       <c r="U59" s="2" t="inlineStr"/>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
@@ -7520,107 +7592,99 @@
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC59" s="2" t="inlineStr">
-        <is>
-          <t>83.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr"/>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A57051D</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>98分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr"/>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N60" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr"/>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7634,7 +7698,7 @@
       <c r="U60" s="2" t="inlineStr"/>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
@@ -7644,65 +7708,65 @@
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB60" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>6/12</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -7735,12 +7799,12 @@
       <c r="N61" s="2" t="inlineStr"/>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7754,7 +7818,7 @@
       <c r="U61" s="2" t="inlineStr"/>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
@@ -7784,41 +7848,45 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC61" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>122.0</t>
+        </is>
+      </c>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7851,12 +7919,12 @@
       <c r="N62" s="2" t="inlineStr"/>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7870,7 +7938,7 @@
       <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
@@ -7895,46 +7963,50 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB62" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC62" s="2" t="inlineStr"/>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7967,12 +8039,12 @@
       <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7986,7 +8058,7 @@
       <c r="U63" s="2" t="inlineStr"/>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
@@ -8011,46 +8083,50 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB63" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC63" s="2" t="inlineStr"/>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -8083,12 +8159,12 @@
       <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8102,7 +8178,7 @@
       <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
@@ -8137,40 +8213,40 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -8203,12 +8279,12 @@
       <c r="N65" s="2" t="inlineStr"/>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8222,7 +8298,7 @@
       <c r="U65" s="2" t="inlineStr"/>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
@@ -8257,40 +8333,40 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A79307D</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -8323,12 +8399,12 @@
       <c r="N66" s="2" t="inlineStr"/>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8342,7 +8418,7 @@
       <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
@@ -8378,35 +8454,35 @@
       <c r="AC66" s="2" t="inlineStr"/>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -8439,12 +8515,12 @@
       <c r="N67" s="2" t="inlineStr"/>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8458,7 +8534,7 @@
       <c r="U67" s="2" t="inlineStr"/>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
@@ -8493,40 +8569,40 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>10/27</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -8559,12 +8635,12 @@
       <c r="N68" s="2" t="inlineStr"/>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8578,7 +8654,7 @@
       <c r="U68" s="2" t="inlineStr"/>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
@@ -8603,46 +8679,50 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB68" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC68" s="2" t="inlineStr"/>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>11/27</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -8675,12 +8755,12 @@
       <c r="N69" s="2" t="inlineStr"/>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8694,7 +8774,7 @@
       <c r="U69" s="2" t="inlineStr"/>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
@@ -8724,17 +8804,13 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC69" s="2" t="inlineStr">
-        <is>
-          <t>86.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr"/>
       <c r="AD69" s="2" t="inlineStr">
         <is>
-          <t>5/12</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -8747,22 +8823,22 @@
       <c r="B70" s="2" t="inlineStr"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -8795,12 +8871,12 @@
       <c r="N70" s="2" t="inlineStr"/>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8814,7 +8890,7 @@
       <c r="U70" s="2" t="inlineStr"/>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
@@ -8839,7 +8915,7 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
@@ -8850,7 +8926,7 @@
       <c r="AC70" s="2" t="inlineStr"/>
       <c r="AD70" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -8863,60 +8939,64 @@
       <c r="B71" s="2" t="inlineStr"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr"/>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N71" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8930,47 +9010,2931 @@
       <c r="U71" s="2" t="inlineStr"/>
       <c r="V71" s="2" t="inlineStr">
         <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="AD71" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr"/>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>08:08</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>83分钟</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr"/>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AD72" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr"/>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>85分钟</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr"/>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AD73" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr"/>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>85分钟</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr"/>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AD74" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr"/>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>08:41</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>81分钟</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr"/>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr"/>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AD75" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr"/>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>80分钟</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr"/>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AD76" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr"/>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr"/>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr"/>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr"/>
+      <c r="AD77" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr"/>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>09:19</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr"/>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AD78" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr"/>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>81分钟</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr"/>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AD79" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr"/>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>85分钟</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr"/>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr"/>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AD80" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr"/>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr"/>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr"/>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="AD81" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr"/>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr"/>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr"/>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr"/>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr"/>
+      <c r="AD82" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr"/>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr"/>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr"/>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr"/>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AD83" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr"/>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr"/>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr"/>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr"/>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr"/>
+      <c r="AD84" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr"/>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr"/>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr"/>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr"/>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AD85" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr"/>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="W71" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr"/>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr"/>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr"/>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="X71" s="2" t="inlineStr">
+      <c r="X86" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="Y71" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Z71" s="2" t="inlineStr">
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA71" s="2" t="inlineStr">
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr"/>
+      <c r="AD86" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr"/>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr"/>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr"/>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr"/>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB71" s="2" t="inlineStr">
+      <c r="AB87" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AC71" s="2" t="inlineStr">
-        <is>
-          <t>83.0</t>
-        </is>
-      </c>
-      <c r="AD71" s="2" t="inlineStr">
-        <is>
-          <t>2/12</t>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AD87" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr"/>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr"/>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr"/>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr"/>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr"/>
+      <c r="AD88" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr"/>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr"/>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr"/>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr"/>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr"/>
+      <c r="AD89" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr"/>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr"/>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr"/>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr"/>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AD90" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr"/>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr"/>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr"/>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr"/>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AD91" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr"/>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr"/>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr"/>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr"/>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr"/>
+      <c r="AD92" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr"/>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr"/>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr"/>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr"/>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="AD93" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr"/>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr"/>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr"/>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr"/>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AD94" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr"/>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr"/>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr"/>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr"/>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AD95" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-25-operations.xlsx
+++ b/data/export/2026-09-25-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD174"/>
+  <dimension ref="A1:AD178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -729,7 +729,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1721,12 +1721,12 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1969,7 +1969,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="AD12" s="2" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -2540,7 +2540,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -3032,7 +3032,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -3280,7 +3280,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3582,7 +3582,7 @@
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -3652,7 +3652,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -4024,7 +4024,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4197,12 +4197,12 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -4768,7 +4768,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4892,7 +4892,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5485,24 +5485,24 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr"/>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5561,12 +5561,12 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -5636,7 +5636,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5733,12 +5733,12 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>68分钟</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr"/>
@@ -5760,7 +5760,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5809,7 +5809,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="AD43" s="2" t="inlineStr">
@@ -5884,7 +5884,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -6004,7 +6004,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -6124,7 +6124,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6364,7 +6364,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6413,12 +6413,12 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6604,7 +6604,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6653,7 +6653,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="AD50" s="2" t="inlineStr">
@@ -6724,7 +6724,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6778,7 +6778,7 @@
       </c>
       <c r="AD51" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -6844,7 +6844,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6898,7 +6898,7 @@
       </c>
       <c r="AD52" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -6964,7 +6964,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -7018,7 +7018,7 @@
       </c>
       <c r="AD53" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -7088,7 +7088,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -7266,7 +7266,7 @@
       </c>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -7336,7 +7336,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7390,7 +7390,7 @@
       </c>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -7584,7 +7584,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7623,14 +7623,14 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB58" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
           <t>130.5</t>
@@ -7638,7 +7638,7 @@
       </c>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -7762,7 +7762,7 @@
       </c>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -7832,7 +7832,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7886,7 +7886,7 @@
       </c>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -7956,7 +7956,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -8005,12 +8005,12 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>129.7</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -8258,7 +8258,7 @@
       </c>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -8328,7 +8328,7 @@
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -8626,7 +8626,7 @@
       </c>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8750,7 +8750,7 @@
       </c>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -8870,7 +8870,7 @@
       </c>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -8940,7 +8940,7 @@
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AD69" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -9118,7 +9118,7 @@
       </c>
       <c r="AD70" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -9188,7 +9188,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="AD71" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -9366,7 +9366,7 @@
       </c>
       <c r="AD72" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -9436,7 +9436,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9490,7 +9490,7 @@
       </c>
       <c r="AD73" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -9560,7 +9560,7 @@
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9614,7 +9614,7 @@
       </c>
       <c r="AD74" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -9734,7 +9734,7 @@
       </c>
       <c r="AD75" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -9858,7 +9858,7 @@
       </c>
       <c r="AD76" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -9928,7 +9928,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9982,7 +9982,7 @@
       </c>
       <c r="AD77" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -10052,7 +10052,7 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -10106,7 +10106,7 @@
       </c>
       <c r="AD78" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -10172,7 +10172,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -10350,7 +10350,7 @@
       </c>
       <c r="AD80" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -10420,7 +10420,7 @@
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -10474,7 +10474,7 @@
       </c>
       <c r="AD81" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -10598,7 +10598,7 @@
       </c>
       <c r="AD82" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -10788,7 +10788,7 @@
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -10827,14 +10827,14 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB84" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
           <t>130.5</t>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="AD84" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -10966,7 +10966,7 @@
       </c>
       <c r="AD85" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -11036,7 +11036,7 @@
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -11085,12 +11085,12 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>129.7</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AD86" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -11156,7 +11156,7 @@
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr">
@@ -11292,7 +11292,7 @@
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -11346,7 +11346,7 @@
       </c>
       <c r="AD88" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -11470,7 +11470,7 @@
       </c>
       <c r="AD89" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -11718,7 +11718,7 @@
       </c>
       <c r="AD91" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -11908,7 +11908,7 @@
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -11962,7 +11962,7 @@
       </c>
       <c r="AD93" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -12086,7 +12086,7 @@
       </c>
       <c r="AD94" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -12210,7 +12210,7 @@
       </c>
       <c r="AD95" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -12280,7 +12280,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -12334,7 +12334,7 @@
       </c>
       <c r="AD96" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -12458,7 +12458,7 @@
       </c>
       <c r="AD97" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -12582,7 +12582,7 @@
       </c>
       <c r="AD98" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -12652,7 +12652,7 @@
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr">
@@ -12706,7 +12706,7 @@
       </c>
       <c r="AD99" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -12830,7 +12830,7 @@
       </c>
       <c r="AD100" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -12900,7 +12900,7 @@
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q101" s="2" t="inlineStr">
@@ -12954,7 +12954,7 @@
       </c>
       <c r="AD101" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -13024,7 +13024,7 @@
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q102" s="2" t="inlineStr">
@@ -13078,7 +13078,7 @@
       </c>
       <c r="AD102" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -13148,7 +13148,7 @@
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -13202,7 +13202,7 @@
       </c>
       <c r="AD103" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -13326,7 +13326,7 @@
       </c>
       <c r="AD104" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -13493,24 +13493,24 @@
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr"/>
       <c r="L106" s="2" t="inlineStr"/>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O106" s="2" t="inlineStr">
@@ -13520,7 +13520,7 @@
       </c>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q106" s="2" t="inlineStr">
@@ -13569,12 +13569,12 @@
       </c>
       <c r="AC106" s="2" t="inlineStr">
         <is>
-          <t>129.7</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AD106" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -13612,7 +13612,7 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程31%处后消失；随后反向物理轨迹由seq37推进至seq45，推进8站，达到≥2站确认条件</t>
+          <t>原方向在全程31%处后消失；随后反向物理轨迹由seq37推进至seq53，推进16站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
@@ -13640,7 +13640,7 @@
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
@@ -13764,7 +13764,7 @@
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr">
@@ -13818,7 +13818,7 @@
       </c>
       <c r="AD108" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -13851,32 +13851,36 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr"/>
       <c r="L109" s="2" t="inlineStr"/>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N109" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -13884,7 +13888,7 @@
       </c>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q109" s="2" t="inlineStr">
@@ -13908,33 +13912,37 @@
       </c>
       <c r="X109" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y109" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z109" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA109" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB109" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB109" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC109" s="2" t="inlineStr"/>
+      <c r="AC109" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AD109" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -14000,7 +14008,7 @@
       </c>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q110" s="2" t="inlineStr">
@@ -14120,7 +14128,7 @@
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q111" s="2" t="inlineStr">
@@ -14236,7 +14244,7 @@
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q112" s="2" t="inlineStr">
@@ -14290,7 +14298,7 @@
       </c>
       <c r="AD112" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -14356,7 +14364,7 @@
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q113" s="2" t="inlineStr">
@@ -14410,7 +14418,7 @@
       </c>
       <c r="AD113" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -14476,7 +14484,7 @@
       </c>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q114" s="2" t="inlineStr">
@@ -14530,7 +14538,7 @@
       </c>
       <c r="AD114" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -14596,7 +14604,7 @@
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q115" s="2" t="inlineStr">
@@ -14650,7 +14658,7 @@
       </c>
       <c r="AD115" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -14716,7 +14724,7 @@
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
@@ -14770,7 +14778,7 @@
       </c>
       <c r="AD116" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -14836,7 +14844,7 @@
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr">
@@ -14890,7 +14898,7 @@
       </c>
       <c r="AD117" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -14956,7 +14964,7 @@
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q118" s="2" t="inlineStr">
@@ -15010,7 +15018,7 @@
       </c>
       <c r="AD118" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -15076,7 +15084,7 @@
       </c>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q119" s="2" t="inlineStr">
@@ -15130,7 +15138,7 @@
       </c>
       <c r="AD119" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -15196,7 +15204,7 @@
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q120" s="2" t="inlineStr">
@@ -15316,7 +15324,7 @@
       </c>
       <c r="P121" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q121" s="2" t="inlineStr">
@@ -15365,40 +15373,40 @@
       </c>
       <c r="AC121" s="2" t="inlineStr">
         <is>
-          <t>129.7</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AD121" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr"/>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
@@ -15431,12 +15439,12 @@
       <c r="N122" s="2" t="inlineStr"/>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q122" s="2" t="inlineStr">
@@ -15450,7 +15458,7 @@
       <c r="U122" s="2" t="inlineStr"/>
       <c r="V122" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="W122" s="2" t="inlineStr">
@@ -15475,7 +15483,7 @@
       </c>
       <c r="AA122" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB122" s="2" t="inlineStr">
@@ -15485,82 +15493,78 @@
       </c>
       <c r="AC122" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AD122" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr"/>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr"/>
       <c r="L123" s="2" t="inlineStr"/>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
-        </is>
-      </c>
-      <c r="N123" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N123" s="2" t="inlineStr"/>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q123" s="2" t="inlineStr">
@@ -15574,7 +15578,7 @@
       <c r="U123" s="2" t="inlineStr"/>
       <c r="V123" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="W123" s="2" t="inlineStr">
@@ -15584,37 +15588,37 @@
       </c>
       <c r="X123" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y123" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z123" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA123" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB123" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AC123" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AD123" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -15627,7 +15631,7 @@
       <c r="B124" s="2" t="inlineStr"/>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
@@ -15637,7 +15641,7 @@
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
@@ -15647,36 +15651,32 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr"/>
       <c r="L124" s="2" t="inlineStr"/>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N124" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N124" s="2" t="inlineStr"/>
       <c r="O124" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -15684,7 +15684,7 @@
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="Q124" s="2" t="inlineStr">
@@ -15698,7 +15698,7 @@
       <c r="U124" s="2" t="inlineStr"/>
       <c r="V124" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="W124" s="2" t="inlineStr">
@@ -15708,17 +15708,17 @@
       </c>
       <c r="X124" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y124" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z124" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA124" s="2" t="inlineStr">
@@ -15728,17 +15728,17 @@
       </c>
       <c r="AB124" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC124" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AD124" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -15751,7 +15751,7 @@
       <c r="B125" s="2" t="inlineStr"/>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
@@ -15761,7 +15761,7 @@
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
@@ -15781,24 +15781,24 @@
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="J125" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr"/>
       <c r="L125" s="2" t="inlineStr"/>
       <c r="M125" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N125" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O125" s="2" t="inlineStr">
@@ -15808,7 +15808,7 @@
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="Q125" s="2" t="inlineStr">
@@ -15822,7 +15822,7 @@
       <c r="U125" s="2" t="inlineStr"/>
       <c r="V125" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W125" s="2" t="inlineStr">
@@ -15847,22 +15847,22 @@
       </c>
       <c r="AA125" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB125" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC125" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AD125" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -15875,7 +15875,7 @@
       <c r="B126" s="2" t="inlineStr"/>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
@@ -15885,7 +15885,7 @@
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
@@ -15905,24 +15905,24 @@
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr"/>
       <c r="L126" s="2" t="inlineStr"/>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N126" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O126" s="2" t="inlineStr">
@@ -15932,7 +15932,7 @@
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="Q126" s="2" t="inlineStr">
@@ -15946,7 +15946,7 @@
       <c r="U126" s="2" t="inlineStr"/>
       <c r="V126" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="W126" s="2" t="inlineStr">
@@ -15976,17 +15976,17 @@
       </c>
       <c r="AB126" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC126" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AD126" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -15999,7 +15999,7 @@
       <c r="B127" s="2" t="inlineStr"/>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
@@ -16009,7 +16009,7 @@
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
@@ -16029,34 +16029,34 @@
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="J127" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="K127" s="2" t="inlineStr"/>
       <c r="L127" s="2" t="inlineStr"/>
       <c r="M127" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N127" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P127" s="2" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="Q127" s="2" t="inlineStr">
@@ -16070,7 +16070,7 @@
       <c r="U127" s="2" t="inlineStr"/>
       <c r="V127" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W127" s="2" t="inlineStr">
@@ -16095,22 +16095,22 @@
       </c>
       <c r="AA127" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB127" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC127" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AD127" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -16123,7 +16123,7 @@
       <c r="B128" s="2" t="inlineStr"/>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
@@ -16133,7 +16133,7 @@
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
@@ -16153,12 +16153,12 @@
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr"/>
@@ -16175,12 +16175,12 @@
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="Q128" s="2" t="inlineStr">
@@ -16194,7 +16194,7 @@
       <c r="U128" s="2" t="inlineStr"/>
       <c r="V128" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="W128" s="2" t="inlineStr">
@@ -16219,22 +16219,22 @@
       </c>
       <c r="AA128" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB128" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC128" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AD128" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -16247,7 +16247,7 @@
       <c r="B129" s="2" t="inlineStr"/>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A66391D</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
@@ -16257,7 +16257,7 @@
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
@@ -16267,32 +16267,36 @@
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="J129" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K129" s="2" t="inlineStr"/>
       <c r="L129" s="2" t="inlineStr"/>
       <c r="M129" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N129" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N129" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -16300,7 +16304,7 @@
       </c>
       <c r="P129" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="Q129" s="2" t="inlineStr">
@@ -16314,7 +16318,7 @@
       <c r="U129" s="2" t="inlineStr"/>
       <c r="V129" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W129" s="2" t="inlineStr">
@@ -16324,37 +16328,37 @@
       </c>
       <c r="X129" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y129" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z129" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA129" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB129" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC129" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AD129" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -16367,7 +16371,7 @@
       <c r="B130" s="2" t="inlineStr"/>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
@@ -16377,7 +16381,7 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
@@ -16397,34 +16401,34 @@
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr"/>
       <c r="L130" s="2" t="inlineStr"/>
       <c r="M130" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N130" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O130" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P130" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="Q130" s="2" t="inlineStr">
@@ -16438,7 +16442,7 @@
       <c r="U130" s="2" t="inlineStr"/>
       <c r="V130" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="W130" s="2" t="inlineStr">
@@ -16463,22 +16467,22 @@
       </c>
       <c r="AA130" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB130" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AC130" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AD130" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -16491,7 +16495,7 @@
       <c r="B131" s="2" t="inlineStr"/>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
@@ -16501,7 +16505,7 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
@@ -16511,44 +16515,40 @@
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J131" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K131" s="2" t="inlineStr"/>
       <c r="L131" s="2" t="inlineStr"/>
       <c r="M131" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
-        </is>
-      </c>
-      <c r="N131" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N131" s="2" t="inlineStr"/>
       <c r="O131" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P131" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="Q131" s="2" t="inlineStr">
@@ -16562,7 +16562,7 @@
       <c r="U131" s="2" t="inlineStr"/>
       <c r="V131" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="W131" s="2" t="inlineStr">
@@ -16572,17 +16572,17 @@
       </c>
       <c r="X131" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y131" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z131" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA131" s="2" t="inlineStr">
@@ -16597,12 +16597,12 @@
       </c>
       <c r="AC131" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AD131" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -16615,24 +16615,24 @@
       <c r="B132" s="2" t="inlineStr"/>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="F132" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -16645,34 +16645,34 @@
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr"/>
       <c r="L132" s="2" t="inlineStr"/>
       <c r="M132" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N132" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O132" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="Q132" s="2" t="inlineStr">
@@ -16686,7 +16686,7 @@
       <c r="U132" s="2" t="inlineStr"/>
       <c r="V132" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="W132" s="2" t="inlineStr">
@@ -16711,22 +16711,22 @@
       </c>
       <c r="AA132" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB132" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC132" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AD132" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -16739,24 +16739,24 @@
       <c r="B133" s="2" t="inlineStr"/>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="F133" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -16769,34 +16769,34 @@
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="J133" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K133" s="2" t="inlineStr"/>
       <c r="L133" s="2" t="inlineStr"/>
       <c r="M133" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N133" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O133" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="P133" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="Q133" s="2" t="inlineStr">
@@ -16810,7 +16810,7 @@
       <c r="U133" s="2" t="inlineStr"/>
       <c r="V133" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="W133" s="2" t="inlineStr">
@@ -16835,22 +16835,22 @@
       </c>
       <c r="AA133" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB133" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC133" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AD133" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -16863,7 +16863,7 @@
       <c r="B134" s="2" t="inlineStr"/>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
@@ -16873,7 +16873,7 @@
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
@@ -16883,40 +16883,44 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr"/>
       <c r="L134" s="2" t="inlineStr"/>
       <c r="M134" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N134" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N134" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O134" s="2" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="Q134" s="2" t="inlineStr">
@@ -16930,7 +16934,7 @@
       <c r="U134" s="2" t="inlineStr"/>
       <c r="V134" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W134" s="2" t="inlineStr">
@@ -16940,17 +16944,17 @@
       </c>
       <c r="X134" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y134" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z134" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA134" s="2" t="inlineStr">
@@ -16960,17 +16964,17 @@
       </c>
       <c r="AB134" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC134" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AD134" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -16983,7 +16987,7 @@
       <c r="B135" s="2" t="inlineStr"/>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
@@ -16993,7 +16997,7 @@
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr">
@@ -17003,32 +17007,36 @@
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="J135" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K135" s="2" t="inlineStr"/>
       <c r="L135" s="2" t="inlineStr"/>
       <c r="M135" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N135" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N135" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O135" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -17036,7 +17044,7 @@
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="Q135" s="2" t="inlineStr">
@@ -17050,7 +17058,7 @@
       <c r="U135" s="2" t="inlineStr"/>
       <c r="V135" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W135" s="2" t="inlineStr">
@@ -17060,37 +17068,37 @@
       </c>
       <c r="X135" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y135" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z135" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA135" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB135" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC135" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AD135" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -17103,22 +17111,22 @@
       <c r="B136" s="2" t="inlineStr"/>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A57022D</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E136" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F136" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
@@ -17151,12 +17159,12 @@
       <c r="N136" s="2" t="inlineStr"/>
       <c r="O136" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="Q136" s="2" t="inlineStr">
@@ -17170,7 +17178,7 @@
       <c r="U136" s="2" t="inlineStr"/>
       <c r="V136" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W136" s="2" t="inlineStr">
@@ -17205,12 +17213,12 @@
       </c>
       <c r="AC136" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AD136" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -17223,64 +17231,60 @@
       <c r="B137" s="2" t="inlineStr"/>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F137" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J137" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K137" s="2" t="inlineStr"/>
       <c r="L137" s="2" t="inlineStr"/>
       <c r="M137" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N137" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N137" s="2" t="inlineStr"/>
       <c r="O137" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P137" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="Q137" s="2" t="inlineStr">
@@ -17294,7 +17298,7 @@
       <c r="U137" s="2" t="inlineStr"/>
       <c r="V137" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="W137" s="2" t="inlineStr">
@@ -17304,22 +17308,22 @@
       </c>
       <c r="X137" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y137" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z137" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA137" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB137" s="2" t="inlineStr">
@@ -17329,12 +17333,12 @@
       </c>
       <c r="AC137" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AD137" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -17347,64 +17351,60 @@
       <c r="B138" s="2" t="inlineStr"/>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F138" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr"/>
       <c r="L138" s="2" t="inlineStr"/>
       <c r="M138" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N138" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N138" s="2" t="inlineStr"/>
       <c r="O138" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="Q138" s="2" t="inlineStr">
@@ -17418,7 +17418,7 @@
       <c r="U138" s="2" t="inlineStr"/>
       <c r="V138" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W138" s="2" t="inlineStr">
@@ -17428,37 +17428,37 @@
       </c>
       <c r="X138" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y138" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z138" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA138" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB138" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC138" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AD138" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -17471,24 +17471,24 @@
       <c r="B139" s="2" t="inlineStr"/>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F139" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -17501,24 +17501,24 @@
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="J139" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="K139" s="2" t="inlineStr"/>
       <c r="L139" s="2" t="inlineStr"/>
       <c r="M139" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N139" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O139" s="2" t="inlineStr">
@@ -17528,7 +17528,7 @@
       </c>
       <c r="P139" s="2" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="Q139" s="2" t="inlineStr">
@@ -17542,7 +17542,7 @@
       <c r="U139" s="2" t="inlineStr"/>
       <c r="V139" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W139" s="2" t="inlineStr">
@@ -17567,22 +17567,22 @@
       </c>
       <c r="AA139" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB139" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB139" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AC139" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AD139" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -17595,7 +17595,7 @@
       <c r="B140" s="2" t="inlineStr"/>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>沪A58633D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
@@ -17605,7 +17605,7 @@
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
@@ -17625,12 +17625,12 @@
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr"/>
@@ -17647,12 +17647,12 @@
       </c>
       <c r="O140" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="Q140" s="2" t="inlineStr">
@@ -17666,7 +17666,7 @@
       <c r="U140" s="2" t="inlineStr"/>
       <c r="V140" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W140" s="2" t="inlineStr">
@@ -17701,12 +17701,12 @@
       </c>
       <c r="AC140" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AD140" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -17719,7 +17719,7 @@
       <c r="B141" s="2" t="inlineStr"/>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A66391D</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
@@ -17729,7 +17729,7 @@
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr">
@@ -17749,7 +17749,7 @@
       </c>
       <c r="I141" s="2" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="J141" s="2" t="inlineStr">
@@ -17761,22 +17761,22 @@
       <c r="L141" s="2" t="inlineStr"/>
       <c r="M141" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N141" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O141" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P141" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="Q141" s="2" t="inlineStr">
@@ -17790,7 +17790,7 @@
       <c r="U141" s="2" t="inlineStr"/>
       <c r="V141" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W141" s="2" t="inlineStr">
@@ -17815,7 +17815,7 @@
       </c>
       <c r="AA141" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB141" s="2" t="inlineStr">
@@ -17825,12 +17825,12 @@
       </c>
       <c r="AC141" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AD141" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -17843,7 +17843,7 @@
       <c r="B142" s="2" t="inlineStr"/>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A58633D</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
@@ -17853,7 +17853,7 @@
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
@@ -17863,40 +17863,44 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr"/>
       <c r="L142" s="2" t="inlineStr"/>
       <c r="M142" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N142" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N142" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O142" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="Q142" s="2" t="inlineStr">
@@ -17910,7 +17914,7 @@
       <c r="U142" s="2" t="inlineStr"/>
       <c r="V142" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W142" s="2" t="inlineStr">
@@ -17920,37 +17924,37 @@
       </c>
       <c r="X142" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y142" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z142" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA142" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB142" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC142" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AD142" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -17963,24 +17967,24 @@
       <c r="B143" s="2" t="inlineStr"/>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A56123D</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="F143" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -17993,12 +17997,12 @@
       </c>
       <c r="I143" s="2" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr"/>
@@ -18015,12 +18019,12 @@
       </c>
       <c r="O143" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="Q143" s="2" t="inlineStr">
@@ -18034,7 +18038,7 @@
       <c r="U143" s="2" t="inlineStr"/>
       <c r="V143" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="W143" s="2" t="inlineStr">
@@ -18059,22 +18063,22 @@
       </c>
       <c r="AA143" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB143" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB143" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AC143" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AD143" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -18087,64 +18091,60 @@
       <c r="B144" s="2" t="inlineStr"/>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
-      <c r="F144" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr"/>
       <c r="L144" s="2" t="inlineStr"/>
       <c r="M144" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N144" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N144" s="2" t="inlineStr"/>
       <c r="O144" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="Q144" s="2" t="inlineStr">
@@ -18158,7 +18158,7 @@
       <c r="U144" s="2" t="inlineStr"/>
       <c r="V144" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="W144" s="2" t="inlineStr">
@@ -18168,37 +18168,37 @@
       </c>
       <c r="X144" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y144" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z144" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA144" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB144" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AC144" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AD144" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -18211,7 +18211,7 @@
       <c r="B145" s="2" t="inlineStr"/>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
@@ -18221,7 +18221,7 @@
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr">
@@ -18241,34 +18241,34 @@
       </c>
       <c r="I145" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr"/>
       <c r="L145" s="2" t="inlineStr"/>
       <c r="M145" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N145" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O145" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P145" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="Q145" s="2" t="inlineStr">
@@ -18282,7 +18282,7 @@
       <c r="U145" s="2" t="inlineStr"/>
       <c r="V145" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W145" s="2" t="inlineStr">
@@ -18307,22 +18307,22 @@
       </c>
       <c r="AA145" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB145" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC145" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AD145" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -18335,24 +18335,24 @@
       <c r="B146" s="2" t="inlineStr"/>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
-        <is>
-          <t>09:55</t>
-        </is>
-      </c>
-      <c r="F146" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -18365,12 +18365,12 @@
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>93分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr"/>
@@ -18387,12 +18387,12 @@
       </c>
       <c r="O146" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P146" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="Q146" s="2" t="inlineStr">
@@ -18406,7 +18406,7 @@
       <c r="U146" s="2" t="inlineStr"/>
       <c r="V146" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="W146" s="2" t="inlineStr">
@@ -18441,12 +18441,12 @@
       </c>
       <c r="AC146" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AD146" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -18459,60 +18459,64 @@
       <c r="B147" s="2" t="inlineStr"/>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="F147" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="J147" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K147" s="2" t="inlineStr"/>
       <c r="L147" s="2" t="inlineStr"/>
       <c r="M147" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N147" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N147" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O147" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P147" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="Q147" s="2" t="inlineStr">
@@ -18526,7 +18530,7 @@
       <c r="U147" s="2" t="inlineStr"/>
       <c r="V147" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="W147" s="2" t="inlineStr">
@@ -18536,37 +18540,37 @@
       </c>
       <c r="X147" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y147" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z147" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA147" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB147" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC147" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AD147" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -18579,7 +18583,7 @@
       <c r="B148" s="2" t="inlineStr"/>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
@@ -18589,7 +18593,7 @@
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr">
@@ -18609,12 +18613,12 @@
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr"/>
@@ -18631,12 +18635,12 @@
       </c>
       <c r="O148" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P148" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="Q148" s="2" t="inlineStr">
@@ -18650,7 +18654,7 @@
       <c r="U148" s="2" t="inlineStr"/>
       <c r="V148" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="W148" s="2" t="inlineStr">
@@ -18675,7 +18679,7 @@
       </c>
       <c r="AA148" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB148" s="2" t="inlineStr">
@@ -18685,12 +18689,12 @@
       </c>
       <c r="AC148" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AD148" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -18703,7 +18707,7 @@
       <c r="B149" s="2" t="inlineStr"/>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
@@ -18713,7 +18717,7 @@
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F149" s="2" t="inlineStr">
@@ -18723,44 +18727,40 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J149" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K149" s="2" t="inlineStr"/>
       <c r="L149" s="2" t="inlineStr"/>
       <c r="M149" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N149" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N149" s="2" t="inlineStr"/>
       <c r="O149" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="P149" s="2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="Q149" s="2" t="inlineStr">
@@ -18774,7 +18774,7 @@
       <c r="U149" s="2" t="inlineStr"/>
       <c r="V149" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="W149" s="2" t="inlineStr">
@@ -18784,17 +18784,17 @@
       </c>
       <c r="X149" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y149" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z149" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA149" s="2" t="inlineStr">
@@ -18804,17 +18804,17 @@
       </c>
       <c r="AB149" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC149" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AD149" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -18827,7 +18827,7 @@
       <c r="B150" s="2" t="inlineStr"/>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
@@ -18837,7 +18837,7 @@
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr">
@@ -18857,12 +18857,12 @@
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="J150" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr"/>
@@ -18879,12 +18879,12 @@
       </c>
       <c r="O150" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="P150" s="2" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="Q150" s="2" t="inlineStr">
@@ -18898,7 +18898,7 @@
       <c r="U150" s="2" t="inlineStr"/>
       <c r="V150" s="2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="W150" s="2" t="inlineStr">
@@ -18923,22 +18923,22 @@
       </c>
       <c r="AA150" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB150" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC150" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AD150" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -18951,7 +18951,7 @@
       <c r="B151" s="2" t="inlineStr"/>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
@@ -18961,7 +18961,7 @@
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr">
@@ -18981,34 +18981,34 @@
       </c>
       <c r="I151" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="J151" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="K151" s="2" t="inlineStr"/>
       <c r="L151" s="2" t="inlineStr"/>
       <c r="M151" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N151" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O151" s="2" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P151" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="Q151" s="2" t="inlineStr">
@@ -19022,7 +19022,7 @@
       <c r="U151" s="2" t="inlineStr"/>
       <c r="V151" s="2" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="W151" s="2" t="inlineStr">
@@ -19052,17 +19052,17 @@
       </c>
       <c r="AB151" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC151" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AD151" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -19075,7 +19075,7 @@
       <c r="B152" s="2" t="inlineStr"/>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A66391D</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
@@ -19085,7 +19085,7 @@
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="F152" s="2" t="inlineStr">
@@ -19105,12 +19105,12 @@
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr"/>
@@ -19127,12 +19127,12 @@
       </c>
       <c r="O152" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P152" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="Q152" s="2" t="inlineStr">
@@ -19146,7 +19146,7 @@
       <c r="U152" s="2" t="inlineStr"/>
       <c r="V152" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="W152" s="2" t="inlineStr">
@@ -19171,7 +19171,7 @@
       </c>
       <c r="AA152" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB152" s="2" t="inlineStr">
@@ -19181,12 +19181,12 @@
       </c>
       <c r="AC152" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AD152" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -19199,7 +19199,7 @@
       <c r="B153" s="2" t="inlineStr"/>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A57022D</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
@@ -19209,7 +19209,7 @@
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="F153" s="2" t="inlineStr">
@@ -19229,34 +19229,34 @@
       </c>
       <c r="I153" s="2" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr"/>
       <c r="L153" s="2" t="inlineStr"/>
       <c r="M153" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N153" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O153" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="P153" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="Q153" s="2" t="inlineStr">
@@ -19270,7 +19270,7 @@
       <c r="U153" s="2" t="inlineStr"/>
       <c r="V153" s="2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="W153" s="2" t="inlineStr">
@@ -19295,22 +19295,22 @@
       </c>
       <c r="AA153" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB153" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC153" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AD153" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -19323,7 +19323,7 @@
       <c r="B154" s="2" t="inlineStr"/>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A56123D</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
@@ -19333,7 +19333,7 @@
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr">
@@ -19353,34 +19353,34 @@
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr"/>
       <c r="L154" s="2" t="inlineStr"/>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N154" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O154" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="P154" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="Q154" s="2" t="inlineStr">
@@ -19394,7 +19394,7 @@
       <c r="U154" s="2" t="inlineStr"/>
       <c r="V154" s="2" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="W154" s="2" t="inlineStr">
@@ -19424,17 +19424,17 @@
       </c>
       <c r="AB154" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC154" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AD154" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -19447,24 +19447,24 @@
       <c r="B155" s="2" t="inlineStr"/>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
-        <is>
-          <t>11:25</t>
-        </is>
-      </c>
-      <c r="F155" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -19477,19 +19477,19 @@
       </c>
       <c r="I155" s="2" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="J155" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr"/>
       <c r="L155" s="2" t="inlineStr"/>
       <c r="M155" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N155" s="2" t="inlineStr">
@@ -19499,12 +19499,12 @@
       </c>
       <c r="O155" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P155" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="Q155" s="2" t="inlineStr">
@@ -19518,7 +19518,7 @@
       <c r="U155" s="2" t="inlineStr"/>
       <c r="V155" s="2" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="W155" s="2" t="inlineStr">
@@ -19543,22 +19543,22 @@
       </c>
       <c r="AA155" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB155" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC155" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AD155" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -19571,24 +19571,24 @@
       <c r="B156" s="2" t="inlineStr"/>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>沪A58633D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
-        <is>
-          <t>11:25</t>
-        </is>
-      </c>
-      <c r="F156" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -19601,34 +19601,34 @@
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr"/>
       <c r="L156" s="2" t="inlineStr"/>
       <c r="M156" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N156" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O156" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="Q156" s="2" t="inlineStr">
@@ -19642,7 +19642,7 @@
       <c r="U156" s="2" t="inlineStr"/>
       <c r="V156" s="2" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="W156" s="2" t="inlineStr">
@@ -19667,22 +19667,22 @@
       </c>
       <c r="AA156" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB156" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC156" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AD156" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -19695,7 +19695,7 @@
       <c r="B157" s="2" t="inlineStr"/>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
@@ -19705,7 +19705,7 @@
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="F157" s="2" t="inlineStr">
@@ -19725,34 +19725,34 @@
       </c>
       <c r="I157" s="2" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr"/>
       <c r="L157" s="2" t="inlineStr"/>
       <c r="M157" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="N157" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O157" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="P157" s="2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="Q157" s="2" t="inlineStr">
@@ -19766,7 +19766,7 @@
       <c r="U157" s="2" t="inlineStr"/>
       <c r="V157" s="2" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="W157" s="2" t="inlineStr">
@@ -19796,17 +19796,17 @@
       </c>
       <c r="AB157" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC157" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AD157" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -19819,7 +19819,7 @@
       <c r="B158" s="2" t="inlineStr"/>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A58633D</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
@@ -19829,7 +19829,7 @@
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr">
@@ -19849,34 +19849,34 @@
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr"/>
       <c r="L158" s="2" t="inlineStr"/>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N158" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O158" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="Q158" s="2" t="inlineStr">
@@ -19890,7 +19890,7 @@
       <c r="U158" s="2" t="inlineStr"/>
       <c r="V158" s="2" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="W158" s="2" t="inlineStr">
@@ -19915,22 +19915,22 @@
       </c>
       <c r="AA158" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB158" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC158" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AD158" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -19943,7 +19943,7 @@
       <c r="B159" s="2" t="inlineStr"/>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
@@ -19953,7 +19953,7 @@
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr">
@@ -19973,34 +19973,34 @@
       </c>
       <c r="I159" s="2" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="J159" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="K159" s="2" t="inlineStr"/>
       <c r="L159" s="2" t="inlineStr"/>
       <c r="M159" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N159" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O159" s="2" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P159" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="Q159" s="2" t="inlineStr">
@@ -20014,7 +20014,7 @@
       <c r="U159" s="2" t="inlineStr"/>
       <c r="V159" s="2" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="W159" s="2" t="inlineStr">
@@ -20044,17 +20044,17 @@
       </c>
       <c r="AB159" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC159" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AD159" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -20067,7 +20067,7 @@
       <c r="B160" s="2" t="inlineStr"/>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
@@ -20077,7 +20077,7 @@
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr">
@@ -20097,12 +20097,12 @@
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="J160" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr"/>
@@ -20119,12 +20119,12 @@
       </c>
       <c r="O160" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P160" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="Q160" s="2" t="inlineStr">
@@ -20138,7 +20138,7 @@
       <c r="U160" s="2" t="inlineStr"/>
       <c r="V160" s="2" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="W160" s="2" t="inlineStr">
@@ -20163,22 +20163,22 @@
       </c>
       <c r="AA160" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB160" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC160" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AD160" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -20191,7 +20191,7 @@
       <c r="B161" s="2" t="inlineStr"/>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A57022D</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
@@ -20201,7 +20201,7 @@
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="F161" s="2" t="inlineStr">
@@ -20221,34 +20221,34 @@
       </c>
       <c r="I161" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="J161" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K161" s="2" t="inlineStr"/>
       <c r="L161" s="2" t="inlineStr"/>
       <c r="M161" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N161" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O161" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="P161" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="Q161" s="2" t="inlineStr">
@@ -20262,7 +20262,7 @@
       <c r="U161" s="2" t="inlineStr"/>
       <c r="V161" s="2" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="W161" s="2" t="inlineStr">
@@ -20287,22 +20287,22 @@
       </c>
       <c r="AA161" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB161" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC161" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AD161" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -20315,7 +20315,7 @@
       <c r="B162" s="2" t="inlineStr"/>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
@@ -20325,7 +20325,7 @@
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr">
@@ -20345,34 +20345,34 @@
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="J162" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr"/>
       <c r="L162" s="2" t="inlineStr"/>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N162" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O162" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="P162" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="Q162" s="2" t="inlineStr">
@@ -20386,7 +20386,7 @@
       <c r="U162" s="2" t="inlineStr"/>
       <c r="V162" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="W162" s="2" t="inlineStr">
@@ -20416,17 +20416,17 @@
       </c>
       <c r="AB162" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC162" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AD162" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -20439,7 +20439,7 @@
       <c r="B163" s="2" t="inlineStr"/>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>沪A58633D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
@@ -20449,7 +20449,7 @@
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="F163" s="2" t="inlineStr">
@@ -20469,34 +20469,34 @@
       </c>
       <c r="I163" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="J163" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K163" s="2" t="inlineStr"/>
       <c r="L163" s="2" t="inlineStr"/>
       <c r="M163" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N163" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O163" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P163" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="Q163" s="2" t="inlineStr">
@@ -20510,7 +20510,7 @@
       <c r="U163" s="2" t="inlineStr"/>
       <c r="V163" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="W163" s="2" t="inlineStr">
@@ -20545,12 +20545,12 @@
       </c>
       <c r="AC163" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AD163" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -20563,7 +20563,7 @@
       <c r="B164" s="2" t="inlineStr"/>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A56123D</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
@@ -20573,7 +20573,7 @@
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="F164" s="2" t="inlineStr">
@@ -20593,12 +20593,12 @@
       </c>
       <c r="I164" s="2" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="J164" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr"/>
@@ -20615,12 +20615,12 @@
       </c>
       <c r="O164" s="2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="P164" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="Q164" s="2" t="inlineStr">
@@ -20634,7 +20634,7 @@
       <c r="U164" s="2" t="inlineStr"/>
       <c r="V164" s="2" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="W164" s="2" t="inlineStr">
@@ -20659,22 +20659,22 @@
       </c>
       <c r="AA164" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB164" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC164" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AD164" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -20687,7 +20687,7 @@
       <c r="B165" s="2" t="inlineStr"/>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A58633D</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
@@ -20697,7 +20697,7 @@
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="F165" s="2" t="inlineStr">
@@ -20707,40 +20707,44 @@
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I165" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="J165" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K165" s="2" t="inlineStr"/>
       <c r="L165" s="2" t="inlineStr"/>
       <c r="M165" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N165" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N165" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O165" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="P165" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="Q165" s="2" t="inlineStr">
@@ -20754,7 +20758,7 @@
       <c r="U165" s="2" t="inlineStr"/>
       <c r="V165" s="2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="W165" s="2" t="inlineStr">
@@ -20764,37 +20768,37 @@
       </c>
       <c r="X165" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y165" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z165" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA165" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB165" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC165" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AD165" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -20807,7 +20811,7 @@
       <c r="B166" s="2" t="inlineStr"/>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
@@ -20817,7 +20821,7 @@
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="F166" s="2" t="inlineStr">
@@ -20827,40 +20831,44 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I166" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="J166" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr"/>
       <c r="L166" s="2" t="inlineStr"/>
       <c r="M166" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N166" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N166" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O166" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="P166" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="Q166" s="2" t="inlineStr">
@@ -20874,7 +20882,7 @@
       <c r="U166" s="2" t="inlineStr"/>
       <c r="V166" s="2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="W166" s="2" t="inlineStr">
@@ -20884,37 +20892,37 @@
       </c>
       <c r="X166" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y166" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z166" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA166" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB166" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AC166" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AD166" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -20927,7 +20935,7 @@
       <c r="B167" s="2" t="inlineStr"/>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
@@ -20937,7 +20945,7 @@
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="F167" s="2" t="inlineStr">
@@ -20947,40 +20955,44 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I167" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="J167" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="K167" s="2" t="inlineStr"/>
       <c r="L167" s="2" t="inlineStr"/>
       <c r="M167" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N167" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N167" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O167" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P167" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="Q167" s="2" t="inlineStr">
@@ -20994,7 +21006,7 @@
       <c r="U167" s="2" t="inlineStr"/>
       <c r="V167" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="W167" s="2" t="inlineStr">
@@ -21004,37 +21016,37 @@
       </c>
       <c r="X167" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y167" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z167" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA167" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB167" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC167" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AD167" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -21047,7 +21059,7 @@
       <c r="B168" s="2" t="inlineStr"/>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
@@ -21057,7 +21069,7 @@
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="F168" s="2" t="inlineStr">
@@ -21067,40 +21079,44 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I168" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="J168" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr"/>
       <c r="L168" s="2" t="inlineStr"/>
       <c r="M168" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N168" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N168" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O168" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P168" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="Q168" s="2" t="inlineStr">
@@ -21114,7 +21130,7 @@
       <c r="U168" s="2" t="inlineStr"/>
       <c r="V168" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="W168" s="2" t="inlineStr">
@@ -21124,17 +21140,17 @@
       </c>
       <c r="X168" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y168" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z168" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA168" s="2" t="inlineStr">
@@ -21144,17 +21160,17 @@
       </c>
       <c r="AB168" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC168" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AD168" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -21167,7 +21183,7 @@
       <c r="B169" s="2" t="inlineStr"/>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
@@ -21177,7 +21193,7 @@
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="F169" s="2" t="inlineStr">
@@ -21215,12 +21231,12 @@
       <c r="N169" s="2" t="inlineStr"/>
       <c r="O169" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="P169" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="Q169" s="2" t="inlineStr">
@@ -21234,7 +21250,7 @@
       <c r="U169" s="2" t="inlineStr"/>
       <c r="V169" s="2" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="W169" s="2" t="inlineStr">
@@ -21264,17 +21280,17 @@
       </c>
       <c r="AB169" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC169" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AD169" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -21287,7 +21303,7 @@
       <c r="B170" s="2" t="inlineStr"/>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
@@ -21297,7 +21313,7 @@
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="F170" s="2" t="inlineStr">
@@ -21335,12 +21351,12 @@
       <c r="N170" s="2" t="inlineStr"/>
       <c r="O170" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="Q170" s="2" t="inlineStr">
@@ -21354,7 +21370,7 @@
       <c r="U170" s="2" t="inlineStr"/>
       <c r="V170" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="W170" s="2" t="inlineStr">
@@ -21379,7 +21395,7 @@
       </c>
       <c r="AA170" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB170" s="2" t="inlineStr">
@@ -21389,12 +21405,12 @@
       </c>
       <c r="AC170" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AD170" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -21407,22 +21423,22 @@
       <c r="B171" s="2" t="inlineStr"/>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A56123D</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E171" s="2" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="F171" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G171" s="2" t="inlineStr">
@@ -21455,12 +21471,12 @@
       <c r="N171" s="2" t="inlineStr"/>
       <c r="O171" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="P171" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="Q171" s="2" t="inlineStr">
@@ -21474,7 +21490,7 @@
       <c r="U171" s="2" t="inlineStr"/>
       <c r="V171" s="2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="W171" s="2" t="inlineStr">
@@ -21504,17 +21520,17 @@
       </c>
       <c r="AB171" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC171" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AD171" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -21527,22 +21543,22 @@
       <c r="B172" s="2" t="inlineStr"/>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E172" s="2" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="F172" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G172" s="2" t="inlineStr">
@@ -21575,12 +21591,12 @@
       <c r="N172" s="2" t="inlineStr"/>
       <c r="O172" s="2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="Q172" s="2" t="inlineStr">
@@ -21594,7 +21610,7 @@
       <c r="U172" s="2" t="inlineStr"/>
       <c r="V172" s="2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="W172" s="2" t="inlineStr">
@@ -21619,22 +21635,22 @@
       </c>
       <c r="AA172" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB172" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB172" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC172" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AD172" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -21647,7 +21663,7 @@
       <c r="B173" s="2" t="inlineStr"/>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
@@ -21657,7 +21673,7 @@
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="F173" s="2" t="inlineStr">
@@ -21695,12 +21711,12 @@
       <c r="N173" s="2" t="inlineStr"/>
       <c r="O173" s="2" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="Q173" s="2" t="inlineStr">
@@ -21714,7 +21730,7 @@
       <c r="U173" s="2" t="inlineStr"/>
       <c r="V173" s="2" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="W173" s="2" t="inlineStr">
@@ -21749,12 +21765,12 @@
       </c>
       <c r="AC173" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AD173" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -21767,7 +21783,7 @@
       <c r="B174" s="2" t="inlineStr"/>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
@@ -21777,7 +21793,7 @@
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="F174" s="2" t="inlineStr">
@@ -21815,12 +21831,12 @@
       <c r="N174" s="2" t="inlineStr"/>
       <c r="O174" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="Q174" s="2" t="inlineStr">
@@ -21834,47 +21850,527 @@
       <c r="U174" s="2" t="inlineStr"/>
       <c r="V174" s="2" t="inlineStr">
         <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="W174" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X174" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y174" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z174" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA174" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB174" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC174" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="AD174" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr"/>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K175" s="2" t="inlineStr"/>
+      <c r="L175" s="2" t="inlineStr"/>
+      <c r="M175" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N175" s="2" t="inlineStr"/>
+      <c r="O175" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="P175" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="Q175" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R175" s="2" t="inlineStr"/>
+      <c r="S175" s="2" t="inlineStr"/>
+      <c r="T175" s="2" t="inlineStr"/>
+      <c r="U175" s="2" t="inlineStr"/>
+      <c r="V175" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="W175" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X175" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y175" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z175" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA175" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB175" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC175" s="2" t="inlineStr">
+        <is>
+          <t>80.5</t>
+        </is>
+      </c>
+      <c r="AD175" s="2" t="inlineStr">
+        <is>
+          <t>5/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr"/>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
           <t>14:55</t>
         </is>
       </c>
-      <c r="W174" s="2" t="inlineStr">
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J176" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K176" s="2" t="inlineStr"/>
+      <c r="L176" s="2" t="inlineStr"/>
+      <c r="M176" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N176" s="2" t="inlineStr"/>
+      <c r="O176" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P176" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="Q176" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R176" s="2" t="inlineStr"/>
+      <c r="S176" s="2" t="inlineStr"/>
+      <c r="T176" s="2" t="inlineStr"/>
+      <c r="U176" s="2" t="inlineStr"/>
+      <c r="V176" s="2" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="W176" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="X174" s="2" t="inlineStr">
+      <c r="X176" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="Y174" s="2" t="inlineStr">
+      <c r="Y176" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Z174" s="2" t="inlineStr">
+      <c r="Z176" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA174" s="2" t="inlineStr">
+      <c r="AA176" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB174" s="2" t="inlineStr">
+      <c r="AB176" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC176" s="2" t="inlineStr">
+        <is>
+          <t>81.7</t>
+        </is>
+      </c>
+      <c r="AD176" s="2" t="inlineStr">
+        <is>
+          <t>8/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr"/>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K177" s="2" t="inlineStr"/>
+      <c r="L177" s="2" t="inlineStr"/>
+      <c r="M177" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N177" s="2" t="inlineStr"/>
+      <c r="O177" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P177" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="Q177" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R177" s="2" t="inlineStr"/>
+      <c r="S177" s="2" t="inlineStr"/>
+      <c r="T177" s="2" t="inlineStr"/>
+      <c r="U177" s="2" t="inlineStr"/>
+      <c r="V177" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="W177" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X177" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y177" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z177" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA177" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB177" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC177" s="2" t="inlineStr">
+        <is>
+          <t>78.4</t>
+        </is>
+      </c>
+      <c r="AD177" s="2" t="inlineStr">
+        <is>
+          <t>3/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr"/>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J178" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K178" s="2" t="inlineStr"/>
+      <c r="L178" s="2" t="inlineStr"/>
+      <c r="M178" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N178" s="2" t="inlineStr"/>
+      <c r="O178" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P178" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="Q178" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R178" s="2" t="inlineStr"/>
+      <c r="S178" s="2" t="inlineStr"/>
+      <c r="T178" s="2" t="inlineStr"/>
+      <c r="U178" s="2" t="inlineStr"/>
+      <c r="V178" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="W178" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X178" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y178" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z178" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA178" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB178" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AC174" s="2" t="inlineStr">
-        <is>
-          <t>84.5</t>
-        </is>
-      </c>
-      <c r="AD174" s="2" t="inlineStr">
-        <is>
-          <t>11/15</t>
+      <c r="AC178" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AD178" s="2" t="inlineStr">
+        <is>
+          <t>15/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-25-operations.xlsx
+++ b/data/export/2026-09-25-operations.xlsx
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -724,17 +724,17 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -982,7 +982,7 @@
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>75.1</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AD7" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1840,17 +1840,17 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1964,17 +1964,17 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2336,17 +2336,17 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>75.1</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AD18" s="2" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -3032,7 +3032,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3076,17 +3076,17 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -3334,7 +3334,7 @@
       </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3448,17 +3448,17 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -3582,7 +3582,7 @@
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -4024,7 +4024,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -4073,7 +4073,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>75.1</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AD29" s="2" t="inlineStr">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4316,17 +4316,17 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -4450,7 +4450,7 @@
       </c>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -4520,7 +4520,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4564,17 +4564,17 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>75.1</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AD36" s="2" t="inlineStr">
@@ -5070,7 +5070,7 @@
       </c>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -5140,7 +5140,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5184,17 +5184,17 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -5388,7 +5388,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5432,17 +5432,17 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -5760,7 +5760,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5804,17 +5804,17 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -6062,7 +6062,7 @@
       </c>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -6256,7 +6256,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6305,7 +6305,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>75.1</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AD47" s="2" t="inlineStr">
@@ -6628,7 +6628,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6672,17 +6672,17 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -6752,7 +6752,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6796,17 +6796,17 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AD51" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="AD52" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -7054,7 +7054,7 @@
       </c>
       <c r="AD53" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -7124,7 +7124,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -7173,7 +7173,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>75.1</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AD54" s="2" t="inlineStr">
@@ -7248,7 +7248,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7292,17 +7292,17 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -7620,7 +7620,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7740,7 +7740,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7784,17 +7784,17 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -7864,7 +7864,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7908,17 +7908,17 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -8166,7 +8166,7 @@
       </c>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -8236,7 +8236,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -8280,17 +8280,17 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -8410,7 +8410,7 @@
       </c>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -8728,7 +8728,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8852,7 +8852,7 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8896,17 +8896,17 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -8976,7 +8976,7 @@
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -9025,7 +9025,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>75.1</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AD69" s="2" t="inlineStr">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -9268,17 +9268,17 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AD71" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -9402,7 +9402,7 @@
       </c>
       <c r="AD72" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -9472,7 +9472,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9516,17 +9516,17 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="AD73" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -9720,7 +9720,7 @@
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9817,24 +9817,24 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>20:59</t>
+          <t>20:56</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr"/>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
@@ -9844,7 +9844,7 @@
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -9893,7 +9893,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>75.1</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AD76" s="2" t="inlineStr">
@@ -9931,32 +9931,36 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:03</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr"/>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N77" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9964,7 +9968,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9988,17 +9992,17 @@
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
@@ -10008,17 +10012,17 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="AD77" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -10051,32 +10055,36 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr"/>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N78" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -10084,7 +10092,7 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -10108,17 +10116,17 @@
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
@@ -10128,17 +10136,17 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AD78" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -10171,32 +10179,36 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:46</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr"/>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N79" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -10204,7 +10216,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -10228,17 +10240,17 @@
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
@@ -10248,17 +10260,17 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="AD79" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -10324,7 +10336,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -10444,7 +10456,7 @@
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -10488,17 +10500,17 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="AD81" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -10618,7 +10630,7 @@
       </c>
       <c r="AD82" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -10812,7 +10824,7 @@
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -10856,17 +10868,17 @@
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>132.7</t>
+          <t>132.8</t>
         </is>
       </c>
       <c r="AD84" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -11308,7 +11320,7 @@
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -11486,7 +11498,7 @@
       </c>
       <c r="AD89" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -11680,7 +11692,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -11804,7 +11816,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -11848,17 +11860,17 @@
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AD92" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -12052,7 +12064,7 @@
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -12096,17 +12108,17 @@
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>135.3</t>
         </is>
       </c>
       <c r="AD94" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -12172,7 +12184,7 @@
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -12226,7 +12238,7 @@
       </c>
       <c r="AD95" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -12296,7 +12308,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -12340,17 +12352,17 @@
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>134.7</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AD96" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -12416,7 +12428,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -12470,7 +12482,7 @@
       </c>
       <c r="AD97" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -12664,7 +12676,7 @@
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr">
@@ -12708,17 +12720,17 @@
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AD99" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -12788,7 +12800,7 @@
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr">
@@ -13280,7 +13292,7 @@
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr">
@@ -13334,7 +13346,7 @@
       </c>
       <c r="AD104" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -13404,7 +13416,7 @@
       </c>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q105" s="2" t="inlineStr">
@@ -13453,12 +13465,12 @@
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>127.3</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AD105" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -13706,7 +13718,7 @@
       </c>
       <c r="AD107" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -13896,7 +13908,7 @@
       </c>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q109" s="2" t="inlineStr">
@@ -14144,7 +14156,7 @@
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q111" s="2" t="inlineStr">
@@ -14188,17 +14200,17 @@
       </c>
       <c r="AB111" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC111" s="2" t="inlineStr">
         <is>
-          <t>132.7</t>
+          <t>132.8</t>
         </is>
       </c>
       <c r="AD111" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -14512,7 +14524,7 @@
       </c>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q114" s="2" t="inlineStr">
@@ -14946,7 +14958,7 @@
       </c>
       <c r="AD117" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -15016,7 +15028,7 @@
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q118" s="2" t="inlineStr">
@@ -15060,17 +15072,17 @@
       </c>
       <c r="AB118" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC118" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AD118" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -15140,7 +15152,7 @@
       </c>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q119" s="2" t="inlineStr">
@@ -15264,7 +15276,7 @@
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q120" s="2" t="inlineStr">
@@ -15308,17 +15320,17 @@
       </c>
       <c r="AB120" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC120" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>135.3</t>
         </is>
       </c>
       <c r="AD120" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -15508,7 +15520,7 @@
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q122" s="2" t="inlineStr">
@@ -15552,17 +15564,17 @@
       </c>
       <c r="AB122" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC122" s="2" t="inlineStr">
         <is>
-          <t>134.7</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AD122" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -15632,7 +15644,7 @@
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q123" s="2" t="inlineStr">
@@ -15686,7 +15698,7 @@
       </c>
       <c r="AD123" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -15756,7 +15768,7 @@
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q124" s="2" t="inlineStr">
@@ -15810,7 +15822,7 @@
       </c>
       <c r="AD124" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -16004,7 +16016,7 @@
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q126" s="2" t="inlineStr">
@@ -16128,7 +16140,7 @@
       </c>
       <c r="P127" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q127" s="2" t="inlineStr">
@@ -16172,17 +16184,17 @@
       </c>
       <c r="AB127" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC127" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AD127" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -16376,7 +16388,7 @@
       </c>
       <c r="P129" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q129" s="2" t="inlineStr">
@@ -16430,7 +16442,7 @@
       </c>
       <c r="AD129" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -16678,7 +16690,7 @@
       </c>
       <c r="AD131" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -16872,7 +16884,7 @@
       </c>
       <c r="P133" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q133" s="2" t="inlineStr">
@@ -17418,7 +17430,7 @@
       </c>
       <c r="AD137" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -17736,7 +17748,7 @@
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q140" s="2" t="inlineStr">
@@ -17790,7 +17802,7 @@
       </c>
       <c r="AD140" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -17984,7 +17996,7 @@
       </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q142" s="2" t="inlineStr">
@@ -18028,17 +18040,17 @@
       </c>
       <c r="AB142" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC142" s="2" t="inlineStr">
         <is>
-          <t>134.7</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AD142" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -18228,7 +18240,7 @@
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q144" s="2" t="inlineStr">
@@ -18406,7 +18418,7 @@
       </c>
       <c r="AD145" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -19472,7 +19484,7 @@
       </c>
       <c r="P154" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q154" s="2" t="inlineStr">
@@ -19516,17 +19528,17 @@
       </c>
       <c r="AB154" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC154" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AD154" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -19720,7 +19732,7 @@
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q156" s="2" t="inlineStr">
@@ -19769,12 +19781,12 @@
       </c>
       <c r="AC156" s="2" t="inlineStr">
         <is>
-          <t>127.3</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AD156" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -19840,7 +19852,7 @@
       </c>
       <c r="P157" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q157" s="2" t="inlineStr">
@@ -19884,17 +19896,17 @@
       </c>
       <c r="AB157" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC157" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>135.3</t>
         </is>
       </c>
       <c r="AD157" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -19964,7 +19976,7 @@
       </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q158" s="2" t="inlineStr">
@@ -20018,7 +20030,7 @@
       </c>
       <c r="AD158" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -20088,7 +20100,7 @@
       </c>
       <c r="P159" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q159" s="2" t="inlineStr">
@@ -20142,7 +20154,7 @@
       </c>
       <c r="AD159" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -20212,7 +20224,7 @@
       </c>
       <c r="P160" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q160" s="2" t="inlineStr">
@@ -20266,7 +20278,7 @@
       </c>
       <c r="AD160" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -20336,7 +20348,7 @@
       </c>
       <c r="P161" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q161" s="2" t="inlineStr">
@@ -20380,17 +20392,17 @@
       </c>
       <c r="AB161" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC161" s="2" t="inlineStr">
         <is>
-          <t>132.7</t>
+          <t>132.8</t>
         </is>
       </c>
       <c r="AD161" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -20456,7 +20468,7 @@
       </c>
       <c r="P162" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q162" s="2" t="inlineStr">
@@ -20580,7 +20592,7 @@
       </c>
       <c r="P163" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q163" s="2" t="inlineStr">
@@ -20704,7 +20716,7 @@
       </c>
       <c r="P164" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q164" s="2" t="inlineStr">
@@ -21002,7 +21014,7 @@
       </c>
       <c r="AD166" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -21196,7 +21208,7 @@
       </c>
       <c r="P168" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q168" s="2" t="inlineStr">
@@ -21250,7 +21262,7 @@
       </c>
       <c r="AD168" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -22151,32 +22163,36 @@
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I176" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="J176" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="K176" s="2" t="inlineStr"/>
       <c r="L176" s="2" t="inlineStr"/>
       <c r="M176" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N176" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N176" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O176" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -22184,7 +22200,7 @@
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q176" s="2" t="inlineStr">
@@ -22208,17 +22224,17 @@
       </c>
       <c r="X176" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y176" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z176" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA176" s="2" t="inlineStr">
@@ -22228,17 +22244,17 @@
       </c>
       <c r="AB176" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC176" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AD176" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -22395,32 +22411,36 @@
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I178" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:58</t>
         </is>
       </c>
       <c r="J178" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="K178" s="2" t="inlineStr"/>
       <c r="L178" s="2" t="inlineStr"/>
       <c r="M178" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N178" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N178" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O178" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -22428,7 +22448,7 @@
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q178" s="2" t="inlineStr">
@@ -22452,17 +22472,17 @@
       </c>
       <c r="X178" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y178" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z178" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA178" s="2" t="inlineStr">
@@ -22472,17 +22492,17 @@
       </c>
       <c r="AB178" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC178" s="2" t="inlineStr">
         <is>
-          <t>134.7</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AD178" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -22525,12 +22545,12 @@
       </c>
       <c r="I179" s="2" t="inlineStr">
         <is>
-          <t>20:55</t>
+          <t>20:58</t>
         </is>
       </c>
       <c r="J179" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="K179" s="2" t="inlineStr"/>
@@ -22552,7 +22572,7 @@
       </c>
       <c r="P179" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q179" s="2" t="inlineStr">
@@ -22601,12 +22621,12 @@
       </c>
       <c r="AC179" s="2" t="inlineStr">
         <is>
-          <t>127.3</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AD179" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -22639,32 +22659,36 @@
       </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I180" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="J180" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="K180" s="2" t="inlineStr"/>
       <c r="L180" s="2" t="inlineStr"/>
       <c r="M180" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N180" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N180" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O180" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -22672,7 +22696,7 @@
       </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q180" s="2" t="inlineStr">
@@ -22696,17 +22720,17 @@
       </c>
       <c r="X180" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y180" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z180" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA180" s="2" t="inlineStr">
@@ -22716,17 +22740,17 @@
       </c>
       <c r="AB180" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC180" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AD180" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -22759,12 +22783,12 @@
       </c>
       <c r="G181" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq30推进至seq64，推进34站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I181" s="2" t="inlineStr">
@@ -22792,7 +22816,7 @@
       </c>
       <c r="P181" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q181" s="2" t="inlineStr">
@@ -22800,10 +22824,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R181" s="2" t="inlineStr"/>
-      <c r="S181" s="2" t="inlineStr"/>
-      <c r="T181" s="2" t="inlineStr"/>
-      <c r="U181" s="2" t="inlineStr"/>
+      <c r="R181" s="2" t="inlineStr">
+        <is>
+          <t>丁香路锦绣路</t>
+        </is>
+      </c>
+      <c r="S181" s="2" t="inlineStr">
+        <is>
+          <t>20:01</t>
+        </is>
+      </c>
+      <c r="T181" s="2" t="inlineStr">
+        <is>
+          <t>20:11</t>
+        </is>
+      </c>
+      <c r="U181" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq29映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±10分钟；反向位置物理seq30（站名待映射） ETA 5分钟参与校验</t>
+        </is>
+      </c>
       <c r="V181" s="2" t="inlineStr">
         <is>
           <t>19:10</t>
@@ -22846,7 +22886,7 @@
       </c>
       <c r="AD181" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -22879,32 +22919,36 @@
       </c>
       <c r="G182" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I182" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:28</t>
         </is>
       </c>
       <c r="J182" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="K182" s="2" t="inlineStr"/>
       <c r="L182" s="2" t="inlineStr"/>
       <c r="M182" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N182" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N182" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O182" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -22912,7 +22956,7 @@
       </c>
       <c r="P182" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q182" s="2" t="inlineStr">
@@ -22936,17 +22980,17 @@
       </c>
       <c r="X182" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y182" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z182" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA182" s="2" t="inlineStr">
@@ -22956,17 +23000,17 @@
       </c>
       <c r="AB182" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC182" s="2" t="inlineStr">
         <is>
-          <t>132.7</t>
+          <t>132.8</t>
         </is>
       </c>
       <c r="AD182" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -22999,32 +23043,36 @@
       </c>
       <c r="G183" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I183" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:34</t>
         </is>
       </c>
       <c r="J183" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="K183" s="2" t="inlineStr"/>
       <c r="L183" s="2" t="inlineStr"/>
       <c r="M183" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N183" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N183" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O183" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -23032,7 +23080,7 @@
       </c>
       <c r="P183" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q183" s="2" t="inlineStr">
@@ -23056,17 +23104,17 @@
       </c>
       <c r="X183" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y183" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z183" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA183" s="2" t="inlineStr">
@@ -23076,17 +23124,17 @@
       </c>
       <c r="AB183" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC183" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>135.3</t>
         </is>
       </c>
       <c r="AD183" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -23152,7 +23200,7 @@
       </c>
       <c r="P184" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q184" s="2" t="inlineStr">
@@ -23206,7 +23254,7 @@
       </c>
       <c r="AD184" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -23239,12 +23287,12 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程46%处后消失；随后反向物理轨迹由seq28推进至seq45，推进17站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I185" s="2" t="inlineStr">
@@ -23272,7 +23320,7 @@
       </c>
       <c r="P185" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q185" s="2" t="inlineStr">
@@ -23280,10 +23328,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R185" s="2" t="inlineStr"/>
-      <c r="S185" s="2" t="inlineStr"/>
-      <c r="T185" s="2" t="inlineStr"/>
-      <c r="U185" s="2" t="inlineStr"/>
+      <c r="R185" s="2" t="inlineStr">
+        <is>
+          <t>物理seq30（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S185" s="2" t="inlineStr">
+        <is>
+          <t>20:36</t>
+        </is>
+      </c>
+      <c r="T185" s="2" t="inlineStr">
+        <is>
+          <t>20:43</t>
+        </is>
+      </c>
+      <c r="U185" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq30映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±7分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="V185" s="2" t="inlineStr">
         <is>
           <t>19:30</t>
@@ -23392,7 +23456,7 @@
       </c>
       <c r="P186" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q186" s="2" t="inlineStr">
@@ -23446,7 +23510,7 @@
       </c>
       <c r="AD186" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -23512,7 +23576,7 @@
       </c>
       <c r="P187" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q187" s="2" t="inlineStr">
@@ -23632,7 +23696,7 @@
       </c>
       <c r="P188" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q188" s="2" t="inlineStr">
@@ -23752,7 +23816,7 @@
       </c>
       <c r="P189" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q189" s="2" t="inlineStr">
@@ -23872,7 +23936,7 @@
       </c>
       <c r="P190" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q190" s="2" t="inlineStr">
@@ -23926,7 +23990,7 @@
       </c>
       <c r="AD190" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -23992,7 +24056,7 @@
       </c>
       <c r="P191" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q191" s="2" t="inlineStr">
@@ -24036,17 +24100,17 @@
       </c>
       <c r="AB191" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC191" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AD191" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -24538,7 +24602,7 @@
       </c>
       <c r="AD195" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -24662,7 +24726,7 @@
       </c>
       <c r="AD196" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -24732,7 +24796,7 @@
       </c>
       <c r="P197" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q197" s="2" t="inlineStr">
@@ -24781,12 +24845,12 @@
       </c>
       <c r="AC197" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AD197" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -24910,7 +24974,7 @@
       </c>
       <c r="AD198" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -25100,7 +25164,7 @@
       </c>
       <c r="P200" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q200" s="2" t="inlineStr">
@@ -25149,12 +25213,12 @@
       </c>
       <c r="AC200" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AD200" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -25224,7 +25288,7 @@
       </c>
       <c r="P201" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q201" s="2" t="inlineStr">
@@ -25273,12 +25337,12 @@
       </c>
       <c r="AC201" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AD201" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -25592,7 +25656,7 @@
       </c>
       <c r="P204" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q204" s="2" t="inlineStr">
@@ -25636,17 +25700,17 @@
       </c>
       <c r="AB204" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC204" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AD204" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -25766,7 +25830,7 @@
       </c>
       <c r="AD205" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -25886,7 +25950,7 @@
       </c>
       <c r="AD206" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -26010,7 +26074,7 @@
       </c>
       <c r="AD207" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -26080,7 +26144,7 @@
       </c>
       <c r="P208" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q208" s="2" t="inlineStr">
@@ -26124,12 +26188,12 @@
       </c>
       <c r="AB208" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC208" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AD208" s="2" t="inlineStr">
@@ -26204,7 +26268,7 @@
       </c>
       <c r="P209" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q209" s="2" t="inlineStr">
@@ -26253,12 +26317,12 @@
       </c>
       <c r="AC209" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AD209" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -26328,7 +26392,7 @@
       </c>
       <c r="P210" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q210" s="2" t="inlineStr">
@@ -26372,17 +26436,17 @@
       </c>
       <c r="AB210" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC210" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AD210" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -26452,7 +26516,7 @@
       </c>
       <c r="P211" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q211" s="2" t="inlineStr">
@@ -26496,17 +26560,17 @@
       </c>
       <c r="AB211" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC211" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AD211" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -26626,7 +26690,7 @@
       </c>
       <c r="AD212" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -26696,7 +26760,7 @@
       </c>
       <c r="P213" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q213" s="2" t="inlineStr">
@@ -26745,12 +26809,12 @@
       </c>
       <c r="AC213" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AD213" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -27122,7 +27186,7 @@
       </c>
       <c r="AD216" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -27188,7 +27252,7 @@
       </c>
       <c r="P217" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q217" s="2" t="inlineStr">
@@ -27237,12 +27301,12 @@
       </c>
       <c r="AC217" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AD217" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -27366,7 +27430,7 @@
       </c>
       <c r="AD218" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -27560,7 +27624,7 @@
       </c>
       <c r="P220" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q220" s="2" t="inlineStr">
@@ -27609,12 +27673,12 @@
       </c>
       <c r="AC220" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AD220" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -27684,7 +27748,7 @@
       </c>
       <c r="P221" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q221" s="2" t="inlineStr">
@@ -27728,17 +27792,17 @@
       </c>
       <c r="AB221" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC221" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AD221" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -27808,7 +27872,7 @@
       </c>
       <c r="P222" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q222" s="2" t="inlineStr">
@@ -27852,17 +27916,17 @@
       </c>
       <c r="AB222" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC222" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AD222" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -27932,7 +27996,7 @@
       </c>
       <c r="P223" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q223" s="2" t="inlineStr">
@@ -27976,12 +28040,12 @@
       </c>
       <c r="AB223" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC223" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AD223" s="2" t="inlineStr">
@@ -28180,7 +28244,7 @@
       </c>
       <c r="P225" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q225" s="2" t="inlineStr">
@@ -28229,12 +28293,12 @@
       </c>
       <c r="AC225" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AD225" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -28304,7 +28368,7 @@
       </c>
       <c r="P226" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q226" s="2" t="inlineStr">
@@ -28348,17 +28412,17 @@
       </c>
       <c r="AB226" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC226" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AD226" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -28676,7 +28740,7 @@
       </c>
       <c r="P229" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q229" s="2" t="inlineStr">
@@ -28720,17 +28784,17 @@
       </c>
       <c r="AB229" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC229" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AD229" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -28854,7 +28918,7 @@
       </c>
       <c r="AD230" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -28924,7 +28988,7 @@
       </c>
       <c r="P231" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q231" s="2" t="inlineStr">
@@ -28968,12 +29032,12 @@
       </c>
       <c r="AB231" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC231" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AD231" s="2" t="inlineStr">
@@ -29048,7 +29112,7 @@
       </c>
       <c r="P232" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q232" s="2" t="inlineStr">
@@ -29092,17 +29156,17 @@
       </c>
       <c r="AB232" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC232" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AD232" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -29172,7 +29236,7 @@
       </c>
       <c r="P233" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q233" s="2" t="inlineStr">
@@ -29216,17 +29280,17 @@
       </c>
       <c r="AB233" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC233" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AD233" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -29296,7 +29360,7 @@
       </c>
       <c r="P234" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q234" s="2" t="inlineStr">
@@ -29340,12 +29404,12 @@
       </c>
       <c r="AB234" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC234" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AD234" s="2" t="inlineStr">
@@ -29598,7 +29662,7 @@
       </c>
       <c r="AD236" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -29722,7 +29786,7 @@
       </c>
       <c r="AD237" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -29846,7 +29910,7 @@
       </c>
       <c r="AD238" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -29916,7 +29980,7 @@
       </c>
       <c r="P239" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q239" s="2" t="inlineStr">
@@ -29960,17 +30024,17 @@
       </c>
       <c r="AB239" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC239" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AD239" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -30040,7 +30104,7 @@
       </c>
       <c r="P240" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q240" s="2" t="inlineStr">
@@ -30089,12 +30153,12 @@
       </c>
       <c r="AC240" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AD240" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -30164,7 +30228,7 @@
       </c>
       <c r="P241" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q241" s="2" t="inlineStr">
@@ -30213,12 +30277,12 @@
       </c>
       <c r="AC241" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AD241" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -30288,7 +30352,7 @@
       </c>
       <c r="P242" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q242" s="2" t="inlineStr">
@@ -30332,12 +30396,12 @@
       </c>
       <c r="AB242" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC242" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AD242" s="2" t="inlineStr">
@@ -30412,7 +30476,7 @@
       </c>
       <c r="P243" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q243" s="2" t="inlineStr">
@@ -30456,17 +30520,17 @@
       </c>
       <c r="AB243" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC243" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AD243" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -30590,7 +30654,7 @@
       </c>
       <c r="AD244" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -30784,7 +30848,7 @@
       </c>
       <c r="P246" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q246" s="2" t="inlineStr">
@@ -30828,12 +30892,12 @@
       </c>
       <c r="AB246" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC246" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AD246" s="2" t="inlineStr">
@@ -30962,7 +31026,7 @@
       </c>
       <c r="AD247" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -31086,7 +31150,7 @@
       </c>
       <c r="AD248" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -31156,7 +31220,7 @@
       </c>
       <c r="P249" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q249" s="2" t="inlineStr">
@@ -31205,12 +31269,12 @@
       </c>
       <c r="AC249" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AD249" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -31280,7 +31344,7 @@
       </c>
       <c r="P250" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q250" s="2" t="inlineStr">
@@ -31329,12 +31393,12 @@
       </c>
       <c r="AC250" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AD250" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -31404,7 +31468,7 @@
       </c>
       <c r="P251" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q251" s="2" t="inlineStr">
@@ -31453,12 +31517,12 @@
       </c>
       <c r="AC251" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AD251" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -31528,7 +31592,7 @@
       </c>
       <c r="P252" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q252" s="2" t="inlineStr">
@@ -31572,17 +31636,17 @@
       </c>
       <c r="AB252" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC252" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AD252" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -31648,7 +31712,7 @@
       </c>
       <c r="P253" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q253" s="2" t="inlineStr">
@@ -31692,17 +31756,17 @@
       </c>
       <c r="AB253" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC253" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AD253" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -31772,7 +31836,7 @@
       </c>
       <c r="P254" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q254" s="2" t="inlineStr">
@@ -31816,17 +31880,17 @@
       </c>
       <c r="AB254" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC254" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AD254" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -31892,7 +31956,7 @@
       </c>
       <c r="P255" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q255" s="2" t="inlineStr">
@@ -31936,12 +32000,12 @@
       </c>
       <c r="AB255" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC255" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AD255" s="2" t="inlineStr">
@@ -32388,7 +32452,7 @@
       </c>
       <c r="P259" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q259" s="2" t="inlineStr">
@@ -32432,12 +32496,12 @@
       </c>
       <c r="AB259" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC259" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AD259" s="2" t="inlineStr">
@@ -32566,7 +32630,7 @@
       </c>
       <c r="AD260" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -32690,7 +32754,7 @@
       </c>
       <c r="AD261" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -32814,7 +32878,7 @@
       </c>
       <c r="AD262" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -32884,7 +32948,7 @@
       </c>
       <c r="P263" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q263" s="2" t="inlineStr">
@@ -32933,12 +32997,12 @@
       </c>
       <c r="AC263" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AD263" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -33008,7 +33072,7 @@
       </c>
       <c r="P264" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q264" s="2" t="inlineStr">
@@ -33052,17 +33116,17 @@
       </c>
       <c r="AB264" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC264" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AD264" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -33132,7 +33196,7 @@
       </c>
       <c r="P265" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q265" s="2" t="inlineStr">
@@ -33176,17 +33240,17 @@
       </c>
       <c r="AB265" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC265" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AD265" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -33256,7 +33320,7 @@
       </c>
       <c r="P266" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q266" s="2" t="inlineStr">
@@ -33305,12 +33369,12 @@
       </c>
       <c r="AC266" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AD266" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -33380,7 +33444,7 @@
       </c>
       <c r="P267" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q267" s="2" t="inlineStr">
@@ -33424,12 +33488,12 @@
       </c>
       <c r="AB267" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC267" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AD267" s="2" t="inlineStr">
@@ -33500,7 +33564,7 @@
       </c>
       <c r="P268" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q268" s="2" t="inlineStr">
@@ -33549,12 +33613,12 @@
       </c>
       <c r="AC268" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AD268" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -33992,7 +34056,7 @@
       </c>
       <c r="P272" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q272" s="2" t="inlineStr">
@@ -34036,17 +34100,17 @@
       </c>
       <c r="AB272" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC272" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AD272" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -34170,7 +34234,7 @@
       </c>
       <c r="AD273" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -34240,7 +34304,7 @@
       </c>
       <c r="P274" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q274" s="2" t="inlineStr">
@@ -34284,12 +34348,12 @@
       </c>
       <c r="AB274" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC274" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AD274" s="2" t="inlineStr">
@@ -34418,7 +34482,7 @@
       </c>
       <c r="AD275" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -34542,7 +34606,7 @@
       </c>
       <c r="AD276" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -34585,24 +34649,24 @@
       </c>
       <c r="I277" s="2" t="inlineStr">
         <is>
-          <t>20:40</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="J277" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K277" s="2" t="inlineStr"/>
       <c r="L277" s="2" t="inlineStr"/>
       <c r="M277" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N277" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O277" s="2" t="inlineStr">
@@ -34612,7 +34676,7 @@
       </c>
       <c r="P277" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q277" s="2" t="inlineStr">
@@ -34661,12 +34725,12 @@
       </c>
       <c r="AC277" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AD277" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -34709,24 +34773,24 @@
       </c>
       <c r="I278" s="2" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="J278" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="K278" s="2" t="inlineStr"/>
       <c r="L278" s="2" t="inlineStr"/>
       <c r="M278" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N278" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O278" s="2" t="inlineStr">
@@ -34736,7 +34800,7 @@
       </c>
       <c r="P278" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q278" s="2" t="inlineStr">
@@ -34785,12 +34849,12 @@
       </c>
       <c r="AC278" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AD278" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -34823,32 +34887,36 @@
       </c>
       <c r="G279" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H279" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I279" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="J279" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K279" s="2" t="inlineStr"/>
       <c r="L279" s="2" t="inlineStr"/>
       <c r="M279" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N279" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N279" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O279" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -34856,7 +34924,7 @@
       </c>
       <c r="P279" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q279" s="2" t="inlineStr">
@@ -34880,17 +34948,17 @@
       </c>
       <c r="X279" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y279" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z279" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA279" s="2" t="inlineStr">
@@ -34900,17 +34968,17 @@
       </c>
       <c r="AB279" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC279" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AD279" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -35073,24 +35141,24 @@
       </c>
       <c r="I281" s="2" t="inlineStr">
         <is>
-          <t>21:02</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="J281" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="K281" s="2" t="inlineStr"/>
       <c r="L281" s="2" t="inlineStr"/>
       <c r="M281" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N281" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O281" s="2" t="inlineStr">
@@ -35100,7 +35168,7 @@
       </c>
       <c r="P281" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q281" s="2" t="inlineStr">
@@ -35149,12 +35217,12 @@
       </c>
       <c r="AC281" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AD281" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -35307,32 +35375,36 @@
       </c>
       <c r="G283" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H283" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I283" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:04</t>
         </is>
       </c>
       <c r="J283" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="K283" s="2" t="inlineStr"/>
       <c r="L283" s="2" t="inlineStr"/>
       <c r="M283" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N283" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N283" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O283" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -35340,7 +35412,7 @@
       </c>
       <c r="P283" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q283" s="2" t="inlineStr">
@@ -35364,17 +35436,17 @@
       </c>
       <c r="X283" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y283" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z283" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA283" s="2" t="inlineStr">
@@ -35384,17 +35456,17 @@
       </c>
       <c r="AB283" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC283" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AD283" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -35427,32 +35499,36 @@
       </c>
       <c r="G284" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H284" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I284" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="J284" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K284" s="2" t="inlineStr"/>
       <c r="L284" s="2" t="inlineStr"/>
       <c r="M284" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N284" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N284" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O284" s="2" t="inlineStr">
         <is>
           <t>12:00</t>
@@ -35460,7 +35536,7 @@
       </c>
       <c r="P284" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q284" s="2" t="inlineStr">
@@ -35484,17 +35560,17 @@
       </c>
       <c r="X284" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y284" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z284" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA284" s="2" t="inlineStr">
@@ -35504,12 +35580,12 @@
       </c>
       <c r="AB284" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC284" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AD284" s="2" t="inlineStr">
@@ -35547,32 +35623,36 @@
       </c>
       <c r="G285" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I285" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:38</t>
         </is>
       </c>
       <c r="J285" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="K285" s="2" t="inlineStr"/>
       <c r="L285" s="2" t="inlineStr"/>
       <c r="M285" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N285" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N285" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O285" s="2" t="inlineStr">
         <is>
           <t>07:50</t>
@@ -35580,7 +35660,7 @@
       </c>
       <c r="P285" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q285" s="2" t="inlineStr">
@@ -35604,17 +35684,17 @@
       </c>
       <c r="X285" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y285" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z285" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA285" s="2" t="inlineStr">
@@ -35624,17 +35704,17 @@
       </c>
       <c r="AB285" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC285" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AD285" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -35667,32 +35747,36 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I286" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:03</t>
         </is>
       </c>
       <c r="J286" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="K286" s="2" t="inlineStr"/>
       <c r="L286" s="2" t="inlineStr"/>
       <c r="M286" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N286" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N286" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O286" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -35700,7 +35784,7 @@
       </c>
       <c r="P286" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q286" s="2" t="inlineStr">
@@ -35724,17 +35808,17 @@
       </c>
       <c r="X286" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y286" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z286" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA286" s="2" t="inlineStr">
@@ -35744,12 +35828,12 @@
       </c>
       <c r="AB286" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC286" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AD286" s="2" t="inlineStr">
@@ -35820,7 +35904,7 @@
       </c>
       <c r="P287" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q287" s="2" t="inlineStr">
@@ -35864,17 +35948,17 @@
       </c>
       <c r="AB287" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC287" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AD287" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -35940,7 +36024,7 @@
       </c>
       <c r="P288" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q288" s="2" t="inlineStr">
@@ -35984,12 +36068,12 @@
       </c>
       <c r="AB288" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC288" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AD288" s="2" t="inlineStr">
